--- a/salidas/empresas/STX.xlsx
+++ b/salidas/empresas/STX.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EPS" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Info" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="EPS" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Info" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,13 +23,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +43,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -48,12 +51,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -435,58 +447,58 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>fecha</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>precio_ajustado</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>precio_cierre</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>volumen</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pe</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>acciones_circulacion</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>market_cap</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>rotacion</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>38748</v>
       </c>
       <c r="B2" t="n">
-        <v>12.51736640930176</v>
+        <v>12.50734233856201</v>
       </c>
       <c r="C2" t="n">
         <v>26.07999992370605</v>
@@ -501,11 +513,11 @@
       <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>38776</v>
       </c>
       <c r="B3" t="n">
-        <v>12.79178428649902</v>
+        <v>12.78153991699219</v>
       </c>
       <c r="C3" t="n">
         <v>26.56999969482422</v>
@@ -520,11 +532,11 @@
       <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>12.67623996734619</v>
+        <v>12.66609287261963</v>
       </c>
       <c r="C4" t="n">
         <v>26.32999992370605</v>
@@ -539,11 +551,11 @@
       <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>38837</v>
       </c>
       <c r="B5" t="n">
-        <v>12.78697109222412</v>
+        <v>12.7767276763916</v>
       </c>
       <c r="C5" t="n">
         <v>26.55999946594238</v>
@@ -558,11 +570,11 @@
       <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>38868</v>
       </c>
       <c r="B6" t="n">
-        <v>11.27527713775635</v>
+        <v>11.26624488830566</v>
       </c>
       <c r="C6" t="n">
         <v>23.35000038146973</v>
@@ -577,11 +589,11 @@
       <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>38898</v>
       </c>
       <c r="B7" t="n">
-        <v>10.93242835998535</v>
+        <v>10.92367458343506</v>
       </c>
       <c r="C7" t="n">
         <v>22.63999938964844</v>
@@ -596,11 +608,11 @@
       <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>38929</v>
       </c>
       <c r="B8" t="n">
-        <v>11.20284748077393</v>
+        <v>11.19387245178223</v>
       </c>
       <c r="C8" t="n">
         <v>23.20000076293945</v>
@@ -615,11 +627,11 @@
       <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>38960</v>
       </c>
       <c r="B9" t="n">
-        <v>10.78568935394287</v>
+        <v>10.77705192565918</v>
       </c>
       <c r="C9" t="n">
         <v>22.25</v>
@@ -634,11 +646,11 @@
       <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>11.19288158416748</v>
+        <v>11.18391704559326</v>
       </c>
       <c r="C10" t="n">
         <v>23.09000015258789</v>
@@ -653,11 +665,11 @@
       <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>39021</v>
       </c>
       <c r="B11" t="n">
-        <v>10.94566249847412</v>
+        <v>10.93689060211182</v>
       </c>
       <c r="C11" t="n">
         <v>22.57999992370605</v>
@@ -672,11 +684,11 @@
       <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>39051</v>
       </c>
       <c r="B12" t="n">
-        <v>12.54271507263184</v>
+        <v>12.53266525268555</v>
       </c>
       <c r="C12" t="n">
         <v>25.76000022888184</v>
@@ -691,11 +703,11 @@
       <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>39082</v>
       </c>
       <c r="B13" t="n">
-        <v>12.90302562713623</v>
+        <v>12.89268684387207</v>
       </c>
       <c r="C13" t="n">
         <v>26.5</v>
@@ -710,11 +722,11 @@
       <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>39113</v>
       </c>
       <c r="B14" t="n">
-        <v>13.23824787139893</v>
+        <v>13.22763919830322</v>
       </c>
       <c r="C14" t="n">
         <v>27.09000015258789</v>
@@ -729,11 +741,11 @@
       <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>39141</v>
       </c>
       <c r="B15" t="n">
-        <v>13.14539813995361</v>
+        <v>13.13486480712891</v>
       </c>
       <c r="C15" t="n">
         <v>26.89999961853027</v>
@@ -748,11 +760,11 @@
       <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>39172</v>
       </c>
       <c r="B16" t="n">
-        <v>11.38616180419922</v>
+        <v>11.37703800201416</v>
       </c>
       <c r="C16" t="n">
         <v>23.29999923706055</v>
@@ -767,11 +779,11 @@
       <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>39202</v>
       </c>
       <c r="B17" t="n">
-        <v>10.82418346405029</v>
+        <v>10.81551456451416</v>
       </c>
       <c r="C17" t="n">
         <v>22.14999961853027</v>
@@ -786,11 +798,11 @@
       <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>39233</v>
       </c>
       <c r="B18" t="n">
-        <v>10.10864925384521</v>
+        <v>10.10055541992188</v>
       </c>
       <c r="C18" t="n">
         <v>20.59000015258789</v>
@@ -805,11 +817,11 @@
       <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>39263</v>
       </c>
       <c r="B19" t="n">
-        <v>10.68796825408936</v>
+        <v>10.67940711975098</v>
       </c>
       <c r="C19" t="n">
         <v>21.77000045776367</v>
@@ -824,11 +836,11 @@
       <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>11.54222393035889</v>
+        <v>11.53297233581543</v>
       </c>
       <c r="C20" t="n">
         <v>23.51000022888184</v>
@@ -843,11 +855,11 @@
       <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>39325</v>
       </c>
       <c r="B21" t="n">
-        <v>12.73046398162842</v>
+        <v>12.72026538848877</v>
       </c>
       <c r="C21" t="n">
         <v>25.81999969482422</v>
@@ -862,11 +874,11 @@
       <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>39355</v>
       </c>
       <c r="B22" t="n">
-        <v>12.61213207244873</v>
+        <v>12.60203456878662</v>
       </c>
       <c r="C22" t="n">
         <v>25.57999992370605</v>
@@ -881,11 +893,11 @@
       <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>39386</v>
       </c>
       <c r="B23" t="n">
-        <v>13.77748584747314</v>
+        <v>13.76644611358643</v>
       </c>
       <c r="C23" t="n">
         <v>27.84000015258789</v>
@@ -900,11 +912,11 @@
       <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>39416</v>
       </c>
       <c r="B24" t="n">
-        <v>12.76297855377197</v>
+        <v>12.75275325775146</v>
       </c>
       <c r="C24" t="n">
         <v>25.79000091552734</v>
@@ -919,11 +931,11 @@
       <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>39447</v>
       </c>
       <c r="B25" t="n">
-        <v>12.61946392059326</v>
+        <v>12.60934925079346</v>
       </c>
       <c r="C25" t="n">
         <v>25.5</v>
@@ -938,11 +950,11 @@
       <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>39478</v>
       </c>
       <c r="B26" t="n">
-        <v>10.0806245803833</v>
+        <v>10.07255077362061</v>
       </c>
       <c r="C26" t="n">
         <v>20.27000045776367</v>
@@ -957,11 +969,11 @@
       <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>39507</v>
       </c>
       <c r="B27" t="n">
-        <v>10.72713565826416</v>
+        <v>10.71854782104492</v>
       </c>
       <c r="C27" t="n">
         <v>21.56999969482422</v>
@@ -976,11 +988,11 @@
       <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>39538</v>
       </c>
       <c r="B28" t="n">
-        <v>10.41383075714111</v>
+        <v>10.40548610687256</v>
       </c>
       <c r="C28" t="n">
         <v>20.94000053405762</v>
@@ -995,11 +1007,11 @@
       <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>39568</v>
       </c>
       <c r="B29" t="n">
-        <v>9.443399429321289</v>
+        <v>9.435839653015137</v>
       </c>
       <c r="C29" t="n">
         <v>18.8700008392334</v>
@@ -1014,11 +1026,11 @@
       <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>10.71953392028809</v>
+        <v>10.71095085144043</v>
       </c>
       <c r="C30" t="n">
         <v>21.42000007629395</v>
@@ -1033,11 +1045,11 @@
       <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>39629</v>
       </c>
       <c r="B31" t="n">
-        <v>9.573515892028809</v>
+        <v>9.565848350524902</v>
       </c>
       <c r="C31" t="n">
         <v>19.1299991607666</v>
@@ -1052,11 +1064,11 @@
       <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>39660</v>
       </c>
       <c r="B32" t="n">
-        <v>7.55167818069458</v>
+        <v>7.545631885528564</v>
       </c>
       <c r="C32" t="n">
         <v>14.97000026702881</v>
@@ -1071,11 +1083,11 @@
       <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>39691</v>
       </c>
       <c r="B33" t="n">
-        <v>7.521413326263428</v>
+        <v>7.515387535095215</v>
       </c>
       <c r="C33" t="n">
         <v>14.90999984741211</v>
@@ -1090,11 +1102,11 @@
       <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>39721</v>
       </c>
       <c r="B34" t="n">
-        <v>6.113984107971191</v>
+        <v>6.10908842086792</v>
       </c>
       <c r="C34" t="n">
         <v>12.11999988555908</v>
@@ -1109,11 +1121,11 @@
       <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>39752</v>
       </c>
       <c r="B35" t="n">
-        <v>3.415154695510864</v>
+        <v>3.412420034408569</v>
       </c>
       <c r="C35" t="n">
         <v>6.769999980926514</v>
@@ -1128,11 +1140,11 @@
       <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>39782</v>
       </c>
       <c r="B36" t="n">
-        <v>2.158144950866699</v>
+        <v>2.156416177749634</v>
       </c>
       <c r="C36" t="n">
         <v>4.210000038146973</v>
@@ -1147,11 +1159,11 @@
       <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>39813</v>
       </c>
       <c r="B37" t="n">
-        <v>2.270922422409058</v>
+        <v>2.269102811813354</v>
       </c>
       <c r="C37" t="n">
         <v>4.429999828338623</v>
@@ -1166,11 +1178,11 @@
       <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>39844</v>
       </c>
       <c r="B38" t="n">
-        <v>1.942842721939087</v>
+        <v>1.941287875175476</v>
       </c>
       <c r="C38" t="n">
         <v>3.789999961853027</v>
@@ -1185,11 +1197,11 @@
       <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>39872</v>
       </c>
       <c r="B39" t="n">
-        <v>2.221682548522949</v>
+        <v>2.219903230667114</v>
       </c>
       <c r="C39" t="n">
         <v>4.300000190734863</v>
@@ -1204,11 +1216,11 @@
       <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>39903</v>
       </c>
       <c r="B40" t="n">
-        <v>3.10519003868103</v>
+        <v>3.102701902389526</v>
       </c>
       <c r="C40" t="n">
         <v>6.010000228881836</v>
@@ -1223,11 +1235,11 @@
       <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>39933</v>
       </c>
       <c r="B41" t="n">
-        <v>4.216031074523926</v>
+        <v>4.212653636932373</v>
       </c>
       <c r="C41" t="n">
         <v>8.159999847412109</v>
@@ -1242,11 +1254,11 @@
       <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>39964</v>
       </c>
       <c r="B42" t="n">
-        <v>4.500199794769287</v>
+        <v>4.49659538269043</v>
       </c>
       <c r="C42" t="n">
         <v>8.710000038146973</v>
@@ -1261,11 +1273,11 @@
       <c r="I42" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>39994</v>
       </c>
       <c r="B43" t="n">
-        <v>5.404372692108154</v>
+        <v>5.400044918060303</v>
       </c>
       <c r="C43" t="n">
         <v>10.46000003814697</v>
@@ -1280,11 +1292,11 @@
       <c r="I43" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>40025</v>
       </c>
       <c r="B44" t="n">
-        <v>6.220712184906006</v>
+        <v>6.215729713439941</v>
       </c>
       <c r="C44" t="n">
         <v>12.03999996185303</v>
@@ -1299,11 +1311,11 @@
       <c r="I44" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>40056</v>
       </c>
       <c r="B45" t="n">
-        <v>7.155885219573975</v>
+        <v>7.150156497955322</v>
       </c>
       <c r="C45" t="n">
         <v>13.85000038146973</v>
@@ -1318,11 +1330,11 @@
       <c r="I45" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>40086</v>
       </c>
       <c r="B46" t="n">
-        <v>7.858559131622314</v>
+        <v>7.852263450622559</v>
       </c>
       <c r="C46" t="n">
         <v>15.21000003814697</v>
@@ -1337,11 +1349,11 @@
       <c r="I46" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>40117</v>
       </c>
       <c r="B47" t="n">
-        <v>7.207552433013916</v>
+        <v>7.201779365539551</v>
       </c>
       <c r="C47" t="n">
         <v>13.94999980926514</v>
@@ -1356,11 +1368,11 @@
       <c r="I47" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>40147</v>
       </c>
       <c r="B48" t="n">
-        <v>7.817222595214844</v>
+        <v>7.810963153839111</v>
       </c>
       <c r="C48" t="n">
         <v>15.13000011444092</v>
@@ -1375,11 +1387,11 @@
       <c r="I48" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>40178</v>
       </c>
       <c r="B49" t="n">
-        <v>9.398232460021973</v>
+        <v>9.390707969665527</v>
       </c>
       <c r="C49" t="n">
         <v>18.19000053405762</v>
@@ -1394,11 +1406,11 @@
       <c r="I49" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>40209</v>
       </c>
       <c r="B50" t="n">
-        <v>8.633562088012695</v>
+        <v>8.626646995544434</v>
       </c>
       <c r="C50" t="n">
         <v>16.70999908447266</v>
@@ -1413,11 +1425,11 @@
       <c r="I50" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>40237</v>
       </c>
       <c r="B51" t="n">
-        <v>10.28690719604492</v>
+        <v>10.27866649627686</v>
       </c>
       <c r="C51" t="n">
         <v>19.90999984741211</v>
@@ -1432,11 +1444,11 @@
       <c r="I51" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>40268</v>
       </c>
       <c r="B52" t="n">
-        <v>9.434404373168945</v>
+        <v>9.426840782165527</v>
       </c>
       <c r="C52" t="n">
         <v>18.26000022888184</v>
@@ -1451,11 +1463,11 @@
       <c r="I52" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>40298</v>
       </c>
       <c r="B53" t="n">
-        <v>9.480898857116699</v>
+        <v>9.473306655883789</v>
       </c>
       <c r="C53" t="n">
         <v>18.35000038146973</v>
@@ -1470,11 +1482,11 @@
       <c r="I53" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>40329</v>
       </c>
       <c r="B54" t="n">
-        <v>7.936056613922119</v>
+        <v>7.929703235626221</v>
       </c>
       <c r="C54" t="n">
         <v>15.35999965667725</v>
@@ -1489,11 +1501,11 @@
       <c r="I54" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>40359</v>
       </c>
       <c r="B55" t="n">
-        <v>6.737381458282471</v>
+        <v>6.731986999511719</v>
       </c>
       <c r="C55" t="n">
         <v>13.03999996185303</v>
@@ -1508,11 +1520,11 @@
       <c r="I55" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>40390</v>
       </c>
       <c r="B56" t="n">
-        <v>6.484214782714844</v>
+        <v>6.479022026062012</v>
       </c>
       <c r="C56" t="n">
         <v>12.55000019073486</v>
@@ -1527,11 +1539,11 @@
       <c r="I56" t="inlineStr"/>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>40421</v>
       </c>
       <c r="B57" t="n">
-        <v>5.239038944244385</v>
+        <v>5.234842300415039</v>
       </c>
       <c r="C57" t="n">
         <v>10.14000034332275</v>
@@ -1546,11 +1558,11 @@
       <c r="I57" t="inlineStr"/>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>40451</v>
       </c>
       <c r="B58" t="n">
-        <v>6.086379051208496</v>
+        <v>6.081502914428711</v>
       </c>
       <c r="C58" t="n">
         <v>11.77999973297119</v>
@@ -1565,11 +1577,11 @@
       <c r="I58" t="inlineStr"/>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>40482</v>
       </c>
       <c r="B59" t="n">
-        <v>7.6002197265625</v>
+        <v>7.594136238098145</v>
       </c>
       <c r="C59" t="n">
         <v>14.71000003814697</v>
@@ -1584,11 +1596,11 @@
       <c r="I59" t="inlineStr"/>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>40512</v>
       </c>
       <c r="B60" t="n">
-        <v>6.92855167388916</v>
+        <v>6.923002243041992</v>
       </c>
       <c r="C60" t="n">
         <v>13.40999984741211</v>
@@ -1609,11 +1621,11 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>40543</v>
       </c>
       <c r="B61" t="n">
-        <v>7.765556812286377</v>
+        <v>7.759337902069092</v>
       </c>
       <c r="C61" t="n">
         <v>15.02999973297119</v>
@@ -1634,11 +1646,11 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>40574</v>
       </c>
       <c r="B62" t="n">
-        <v>7.233388900756836</v>
+        <v>7.22758960723877</v>
       </c>
       <c r="C62" t="n">
         <v>14</v>
@@ -1659,11 +1671,11 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="B63" t="n">
-        <v>6.561715602874756</v>
+        <v>6.556461334228516</v>
       </c>
       <c r="C63" t="n">
         <v>12.69999980926514</v>
@@ -1684,11 +1696,11 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>40633</v>
       </c>
       <c r="B64" t="n">
-        <v>7.445220947265625</v>
+        <v>7.439258575439453</v>
       </c>
       <c r="C64" t="n">
         <v>14.40999984741211</v>
@@ -1709,11 +1721,11 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>40663</v>
       </c>
       <c r="B65" t="n">
-        <v>9.19589900970459</v>
+        <v>9.188530921936035</v>
       </c>
       <c r="C65" t="n">
         <v>17.6200008392334</v>
@@ -1734,11 +1746,11 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>40694</v>
       </c>
       <c r="B66" t="n">
-        <v>8.767935752868652</v>
+        <v>8.760915756225586</v>
       </c>
       <c r="C66" t="n">
         <v>16.79999923706055</v>
@@ -1759,11 +1771,11 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>40724</v>
       </c>
       <c r="B67" t="n">
-        <v>8.43392276763916</v>
+        <v>8.427167892456055</v>
       </c>
       <c r="C67" t="n">
         <v>16.15999984741211</v>
@@ -1784,11 +1796,11 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>40755</v>
       </c>
       <c r="B68" t="n">
-        <v>7.24920654296875</v>
+        <v>7.243398189544678</v>
       </c>
       <c r="C68" t="n">
         <v>13.89000034332275</v>
@@ -1809,11 +1821,11 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>40786</v>
       </c>
       <c r="B69" t="n">
-        <v>6.127165794372559</v>
+        <v>6.12225866317749</v>
       </c>
       <c r="C69" t="n">
         <v>11.57999992370605</v>
@@ -1838,11 +1850,11 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>40816</v>
       </c>
       <c r="B70" t="n">
-        <v>5.439316272735596</v>
+        <v>5.434958457946777</v>
       </c>
       <c r="C70" t="n">
         <v>10.27999973297119</v>
@@ -1867,11 +1879,11 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>40847</v>
       </c>
       <c r="B71" t="n">
-        <v>8.545225143432617</v>
+        <v>8.538382530212402</v>
       </c>
       <c r="C71" t="n">
         <v>16.14999961853027</v>
@@ -1896,11 +1908,11 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>40877</v>
       </c>
       <c r="B72" t="n">
-        <v>9.14986515045166</v>
+        <v>9.142539978027344</v>
       </c>
       <c r="C72" t="n">
         <v>17.10000038146973</v>
@@ -1925,11 +1937,11 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>40908</v>
       </c>
       <c r="B73" t="n">
-        <v>8.775313377380371</v>
+        <v>8.768282890319824</v>
       </c>
       <c r="C73" t="n">
         <v>16.39999961853027</v>
@@ -1954,11 +1966,11 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>40939</v>
       </c>
       <c r="B74" t="n">
-        <v>11.31159591674805</v>
+        <v>11.30253124237061</v>
       </c>
       <c r="C74" t="n">
         <v>21.13999938964844</v>
@@ -1983,11 +1995,11 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>40968</v>
       </c>
       <c r="B75" t="n">
-        <v>14.18657112121582</v>
+        <v>14.17520999908447</v>
       </c>
       <c r="C75" t="n">
         <v>26.26000022888184</v>
@@ -2012,11 +2024,11 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>40999</v>
       </c>
       <c r="B76" t="n">
-        <v>14.56473350524902</v>
+        <v>14.55307006835938</v>
       </c>
       <c r="C76" t="n">
         <v>26.95999908447266</v>
@@ -2041,11 +2053,11 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>41029</v>
       </c>
       <c r="B77" t="n">
-        <v>16.7592716217041</v>
+        <v>16.74585151672363</v>
       </c>
       <c r="C77" t="n">
         <v>30.76000022888184</v>
@@ -2070,11 +2082,11 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>41060</v>
       </c>
       <c r="B78" t="n">
-        <v>12.76559829711914</v>
+        <v>12.75537014007568</v>
       </c>
       <c r="C78" t="n">
         <v>23.43000030517578</v>
@@ -2099,11 +2111,11 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>41090</v>
       </c>
       <c r="B79" t="n">
-        <v>13.47388648986816</v>
+        <v>13.46309947967529</v>
       </c>
       <c r="C79" t="n">
         <v>24.72999954223633</v>
@@ -2128,11 +2140,11 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>41121</v>
       </c>
       <c r="B80" t="n">
-        <v>16.35609245300293</v>
+        <v>16.34298706054688</v>
       </c>
       <c r="C80" t="n">
         <v>30.02000045776367</v>
@@ -2157,11 +2169,11 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>41152</v>
       </c>
       <c r="B81" t="n">
-        <v>17.61062812805176</v>
+        <v>17.59652137756348</v>
       </c>
       <c r="C81" t="n">
         <v>32.0099983215332</v>
@@ -2186,11 +2198,11 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>41182</v>
       </c>
       <c r="B82" t="n">
-        <v>17.032958984375</v>
+        <v>17.01931190490723</v>
       </c>
       <c r="C82" t="n">
         <v>30.95999908447266</v>
@@ -2215,11 +2227,11 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>41213</v>
       </c>
       <c r="B83" t="n">
-        <v>15.03587341308594</v>
+        <v>15.02383995056152</v>
       </c>
       <c r="C83" t="n">
         <v>27.32999992370605</v>
@@ -2244,11 +2256,11 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>41243</v>
       </c>
       <c r="B84" t="n">
-        <v>13.95988655090332</v>
+        <v>13.94870662689209</v>
       </c>
       <c r="C84" t="n">
         <v>25.10000038146973</v>
@@ -2273,11 +2285,11 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>41274</v>
       </c>
       <c r="B85" t="n">
-        <v>17.14311599731445</v>
+        <v>17.12938499450684</v>
       </c>
       <c r="C85" t="n">
         <v>30.42000007629395</v>
@@ -2302,11 +2314,11 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>41305</v>
       </c>
       <c r="B86" t="n">
-        <v>19.14934730529785</v>
+        <v>19.13400459289551</v>
       </c>
       <c r="C86" t="n">
         <v>33.97999954223633</v>
@@ -2331,11 +2343,11 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>41333</v>
       </c>
       <c r="B87" t="n">
-        <v>18.12368774414062</v>
+        <v>18.10917091369629</v>
       </c>
       <c r="C87" t="n">
         <v>32.15999984741211</v>
@@ -2360,11 +2372,11 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>41364</v>
       </c>
       <c r="B88" t="n">
-        <v>20.60330390930176</v>
+        <v>20.58679962158203</v>
       </c>
       <c r="C88" t="n">
         <v>36.56000137329102</v>
@@ -2389,11 +2401,11 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>41394</v>
       </c>
       <c r="B89" t="n">
-        <v>20.68219184875488</v>
+        <v>20.66562843322754</v>
       </c>
       <c r="C89" t="n">
         <v>36.70000076293945</v>
@@ -2418,11 +2430,11 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>41425</v>
       </c>
       <c r="B90" t="n">
-        <v>24.50758361816406</v>
+        <v>24.48794364929199</v>
       </c>
       <c r="C90" t="n">
         <v>43.08000183105469</v>
@@ -2447,11 +2459,11 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="2" t="n">
         <v>41455</v>
       </c>
       <c r="B91" t="n">
-        <v>25.50313758850098</v>
+        <v>25.48269844055176</v>
       </c>
       <c r="C91" t="n">
         <v>44.83000183105469</v>
@@ -2476,11 +2488,11 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="2" t="n">
         <v>41486</v>
       </c>
       <c r="B92" t="n">
-        <v>23.27309226989746</v>
+        <v>23.25446128845215</v>
       </c>
       <c r="C92" t="n">
         <v>40.90999984741211</v>
@@ -2505,11 +2517,11 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="2" t="n">
         <v>41517</v>
       </c>
       <c r="B93" t="n">
-        <v>22.00311470031738</v>
+        <v>21.98549270629883</v>
       </c>
       <c r="C93" t="n">
         <v>38.31999969482422</v>
@@ -2534,11 +2546,11 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="2" t="n">
         <v>41547</v>
       </c>
       <c r="B94" t="n">
-        <v>25.12672996520996</v>
+        <v>25.10660552978516</v>
       </c>
       <c r="C94" t="n">
         <v>43.7599983215332</v>
@@ -2563,11 +2575,11 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="2" t="n">
         <v>41578</v>
       </c>
       <c r="B95" t="n">
-        <v>27.95751762390137</v>
+        <v>27.93511581420898</v>
       </c>
       <c r="C95" t="n">
         <v>48.68999862670898</v>
@@ -2592,11 +2604,11 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" s="2" t="n">
         <v>41608</v>
       </c>
       <c r="B96" t="n">
-        <v>28.4105224609375</v>
+        <v>28.38776969909668</v>
       </c>
       <c r="C96" t="n">
         <v>49.04000091552734</v>
@@ -2621,11 +2633,11 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="2" t="n">
         <v>41639</v>
       </c>
       <c r="B97" t="n">
-        <v>32.53538131713867</v>
+        <v>32.50933074951172</v>
       </c>
       <c r="C97" t="n">
         <v>56.15999984741211</v>
@@ -2650,11 +2662,11 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" s="2" t="n">
         <v>41670</v>
       </c>
       <c r="B98" t="n">
-        <v>30.62358093261719</v>
+        <v>30.59904670715332</v>
       </c>
       <c r="C98" t="n">
         <v>52.86000061035156</v>
@@ -2679,11 +2691,11 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" s="2" t="n">
         <v>41698</v>
       </c>
       <c r="B99" t="n">
-        <v>30.50250053405762</v>
+        <v>30.47806930541992</v>
       </c>
       <c r="C99" t="n">
         <v>52.18999862670898</v>
@@ -2708,11 +2720,11 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" s="2" t="n">
         <v>41729</v>
       </c>
       <c r="B100" t="n">
-        <v>32.82276916503906</v>
+        <v>32.79647445678711</v>
       </c>
       <c r="C100" t="n">
         <v>56.15999984741211</v>
@@ -2737,11 +2749,11 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" s="2" t="n">
         <v>41759</v>
       </c>
       <c r="B101" t="n">
-        <v>30.73043251037598</v>
+        <v>30.70582580566406</v>
       </c>
       <c r="C101" t="n">
         <v>52.58000183105469</v>
@@ -2766,11 +2778,11 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" s="2" t="n">
         <v>41790</v>
       </c>
       <c r="B102" t="n">
-        <v>31.67745018005371</v>
+        <v>31.65206527709961</v>
       </c>
       <c r="C102" t="n">
         <v>53.72999954223633</v>
@@ -2795,11 +2807,11 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" s="2" t="n">
         <v>41820</v>
       </c>
       <c r="B103" t="n">
-        <v>33.49921417236328</v>
+        <v>33.47238540649414</v>
       </c>
       <c r="C103" t="n">
         <v>56.81999969482422</v>
@@ -2824,11 +2836,11 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" s="2" t="n">
         <v>41851</v>
       </c>
       <c r="B104" t="n">
-        <v>34.54864501953125</v>
+        <v>34.52097702026367</v>
       </c>
       <c r="C104" t="n">
         <v>58.59999847412109</v>
@@ -2853,11 +2865,11 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" s="2" t="n">
         <v>41882</v>
       </c>
       <c r="B105" t="n">
-        <v>37.17371368408203</v>
+        <v>37.14392471313477</v>
       </c>
       <c r="C105" t="n">
         <v>62.58000183105469</v>
@@ -2882,11 +2894,11 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" s="2" t="n">
         <v>41912</v>
       </c>
       <c r="B106" t="n">
-        <v>34.01945495605469</v>
+        <v>33.99220657348633</v>
       </c>
       <c r="C106" t="n">
         <v>57.27000045776367</v>
@@ -2911,11 +2923,11 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" s="2" t="n">
         <v>41943</v>
       </c>
       <c r="B107" t="n">
-        <v>37.32221221923828</v>
+        <v>37.29232025146484</v>
       </c>
       <c r="C107" t="n">
         <v>62.83000183105469</v>
@@ -2940,11 +2952,11 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" s="2" t="n">
         <v>41973</v>
       </c>
       <c r="B108" t="n">
-        <v>39.60607147216797</v>
+        <v>39.5743522644043</v>
       </c>
       <c r="C108" t="n">
         <v>66.11000061035156</v>
@@ -2969,11 +2981,11 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" s="2" t="n">
         <v>42004</v>
       </c>
       <c r="B109" t="n">
-        <v>39.83972930908203</v>
+        <v>39.80781555175781</v>
       </c>
       <c r="C109" t="n">
         <v>66.5</v>
@@ -2998,11 +3010,11 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" s="2" t="n">
         <v>42035</v>
       </c>
       <c r="B110" t="n">
-        <v>33.81283187866211</v>
+        <v>33.78574371337891</v>
       </c>
       <c r="C110" t="n">
         <v>56.43999862670898</v>
@@ -3027,11 +3039,11 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" s="2" t="n">
         <v>42063</v>
       </c>
       <c r="B111" t="n">
-        <v>36.94687271118164</v>
+        <v>36.91727447509766</v>
       </c>
       <c r="C111" t="n">
         <v>61.11999893188477</v>
@@ -3056,11 +3068,11 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" s="2" t="n">
         <v>42094</v>
       </c>
       <c r="B112" t="n">
-        <v>31.45198059082031</v>
+        <v>31.42679214477539</v>
       </c>
       <c r="C112" t="n">
         <v>52.02999877929688</v>
@@ -3085,11 +3097,11 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" s="2" t="n">
         <v>42124</v>
       </c>
       <c r="B113" t="n">
-        <v>35.82394790649414</v>
+        <v>35.79525375366211</v>
       </c>
       <c r="C113" t="n">
         <v>58.72000122070312</v>
@@ -3114,11 +3126,11 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" s="2" t="n">
         <v>42155</v>
       </c>
       <c r="B114" t="n">
-        <v>33.94489669799805</v>
+        <v>33.917724609375</v>
       </c>
       <c r="C114" t="n">
         <v>55.63999938964844</v>
@@ -3143,11 +3155,11 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" s="2" t="n">
         <v>42185</v>
       </c>
       <c r="B115" t="n">
-        <v>28.97884368896484</v>
+        <v>28.95562744140625</v>
       </c>
       <c r="C115" t="n">
         <v>47.5</v>
@@ -3172,11 +3184,11 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" s="2" t="n">
         <v>42216</v>
       </c>
       <c r="B116" t="n">
-        <v>30.87008666992188</v>
+        <v>30.84537696838379</v>
       </c>
       <c r="C116" t="n">
         <v>50.59999847412109</v>
@@ -3201,11 +3213,11 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" s="2" t="n">
         <v>42247</v>
       </c>
       <c r="B117" t="n">
-        <v>31.69163131713867</v>
+        <v>31.66623497009277</v>
       </c>
       <c r="C117" t="n">
         <v>51.40000152587891</v>
@@ -3230,11 +3242,11 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" s="2" t="n">
         <v>42277</v>
       </c>
       <c r="B118" t="n">
-        <v>27.62226486206055</v>
+        <v>27.60013961791992</v>
       </c>
       <c r="C118" t="n">
         <v>44.79999923706055</v>
@@ -3259,11 +3271,11 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" s="2" t="n">
         <v>42308</v>
       </c>
       <c r="B119" t="n">
-        <v>23.46660041809082</v>
+        <v>23.44780731201172</v>
       </c>
       <c r="C119" t="n">
         <v>38.06000137329102</v>
@@ -3288,11 +3300,11 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" s="2" t="n">
         <v>42338</v>
       </c>
       <c r="B120" t="n">
-        <v>22.51076698303223</v>
+        <v>22.49273300170898</v>
       </c>
       <c r="C120" t="n">
         <v>35.93999862670898</v>
@@ -3317,11 +3329,11 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" s="2" t="n">
         <v>42369</v>
       </c>
       <c r="B121" t="n">
-        <v>22.96173477172852</v>
+        <v>22.94334983825684</v>
       </c>
       <c r="C121" t="n">
         <v>36.65999984741211</v>
@@ -3346,11 +3358,11 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" s="2" t="n">
         <v>42400</v>
       </c>
       <c r="B122" t="n">
-        <v>18.19526290893555</v>
+        <v>18.18069267272949</v>
       </c>
       <c r="C122" t="n">
         <v>29.04999923706055</v>
@@ -3375,11 +3387,11 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" s="2" t="n">
         <v>42429</v>
       </c>
       <c r="B123" t="n">
-        <v>20.03421211242676</v>
+        <v>20.01816749572754</v>
       </c>
       <c r="C123" t="n">
         <v>31.36000061035156</v>
@@ -3404,11 +3416,11 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" s="2" t="n">
         <v>42460</v>
       </c>
       <c r="B124" t="n">
-        <v>22.00825119018555</v>
+        <v>21.99062156677246</v>
       </c>
       <c r="C124" t="n">
         <v>34.45000076293945</v>
@@ -3433,11 +3445,11 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
+      <c r="A125" s="2" t="n">
         <v>42490</v>
       </c>
       <c r="B125" t="n">
-        <v>13.90767669677734</v>
+        <v>13.89653873443604</v>
       </c>
       <c r="C125" t="n">
         <v>21.77000045776367</v>
@@ -3462,11 +3474,11 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
+      <c r="A126" s="2" t="n">
         <v>42521</v>
       </c>
       <c r="B126" t="n">
-        <v>14.88088321685791</v>
+        <v>14.86896419525146</v>
       </c>
       <c r="C126" t="n">
         <v>22.55999946594238</v>
@@ -3491,11 +3503,11 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="n">
+      <c r="A127" s="2" t="n">
         <v>42551</v>
       </c>
       <c r="B127" t="n">
-        <v>16.06818771362305</v>
+        <v>16.05531883239746</v>
       </c>
       <c r="C127" t="n">
         <v>24.36000061035156</v>
@@ -3520,11 +3532,11 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="n">
+      <c r="A128" s="2" t="n">
         <v>42582</v>
       </c>
       <c r="B128" t="n">
-        <v>21.12742042541504</v>
+        <v>21.11049461364746</v>
       </c>
       <c r="C128" t="n">
         <v>32.02999877929688</v>
@@ -3549,11 +3561,11 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="n">
+      <c r="A129" s="2" t="n">
         <v>42613</v>
       </c>
       <c r="B129" t="n">
-        <v>22.25536155700684</v>
+        <v>22.2375373840332</v>
       </c>
       <c r="C129" t="n">
         <v>33.7400016784668</v>
@@ -3578,11 +3590,11 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="n">
+      <c r="A130" s="2" t="n">
         <v>42643</v>
       </c>
       <c r="B130" t="n">
-        <v>25.8759593963623</v>
+        <v>25.85522651672363</v>
       </c>
       <c r="C130" t="n">
         <v>38.54999923706055</v>
@@ -3607,11 +3619,11 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="n">
+      <c r="A131" s="2" t="n">
         <v>42674</v>
       </c>
       <c r="B131" t="n">
-        <v>23.02993965148926</v>
+        <v>23.01148796081543</v>
       </c>
       <c r="C131" t="n">
         <v>34.31000137329102</v>
@@ -3636,11 +3648,11 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="1" t="n">
+      <c r="A132" s="2" t="n">
         <v>42704</v>
       </c>
       <c r="B132" t="n">
-        <v>26.91636085510254</v>
+        <v>26.89480972290039</v>
       </c>
       <c r="C132" t="n">
         <v>40.09999847412109</v>
@@ -3665,11 +3677,11 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="1" t="n">
+      <c r="A133" s="2" t="n">
         <v>42735</v>
       </c>
       <c r="B133" t="n">
-        <v>26.04046058654785</v>
+        <v>26.01960182189941</v>
       </c>
       <c r="C133" t="n">
         <v>38.16999816894531</v>
@@ -3694,11 +3706,11 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="n">
+      <c r="A134" s="2" t="n">
         <v>42766</v>
       </c>
       <c r="B134" t="n">
-        <v>30.8023853302002</v>
+        <v>30.7777156829834</v>
       </c>
       <c r="C134" t="n">
         <v>45.15000152587891</v>
@@ -3723,11 +3735,11 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="n">
+      <c r="A135" s="2" t="n">
         <v>42794</v>
       </c>
       <c r="B135" t="n">
-        <v>32.87633514404297</v>
+        <v>32.85000228881836</v>
       </c>
       <c r="C135" t="n">
         <v>48.18999862670898</v>
@@ -3752,11 +3764,11 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="n">
+      <c r="A136" s="2" t="n">
         <v>42825</v>
       </c>
       <c r="B136" t="n">
-        <v>31.76143836975098</v>
+        <v>31.73599433898926</v>
       </c>
       <c r="C136" t="n">
         <v>45.93000030517578</v>
@@ -3781,11 +3793,11 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="1" t="n">
+      <c r="A137" s="2" t="n">
         <v>42855</v>
       </c>
       <c r="B137" t="n">
-        <v>29.13367080688477</v>
+        <v>29.11033058166504</v>
       </c>
       <c r="C137" t="n">
         <v>42.13000106811523</v>
@@ -3810,11 +3822,11 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="1" t="n">
+      <c r="A138" s="2" t="n">
         <v>42886</v>
       </c>
       <c r="B138" t="n">
-        <v>30.12945175170898</v>
+        <v>30.10531234741211</v>
       </c>
       <c r="C138" t="n">
         <v>43.56999969482422</v>
@@ -3839,11 +3851,11 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="1" t="n">
+      <c r="A139" s="2" t="n">
         <v>42916</v>
       </c>
       <c r="B139" t="n">
-        <v>27.20410537719727</v>
+        <v>27.18231391906738</v>
       </c>
       <c r="C139" t="n">
         <v>38.75</v>
@@ -3868,11 +3880,11 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="1" t="n">
+      <c r="A140" s="2" t="n">
         <v>42947</v>
       </c>
       <c r="B140" t="n">
-        <v>23.1392822265625</v>
+        <v>23.12075424194336</v>
       </c>
       <c r="C140" t="n">
         <v>32.95999908447266</v>
@@ -3897,11 +3909,11 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="1" t="n">
+      <c r="A141" s="2" t="n">
         <v>42978</v>
       </c>
       <c r="B141" t="n">
-        <v>22.1353645324707</v>
+        <v>22.11763763427734</v>
       </c>
       <c r="C141" t="n">
         <v>31.53000068664551</v>
@@ -3926,11 +3938,11 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="1" t="n">
+      <c r="A142" s="2" t="n">
         <v>43008</v>
       </c>
       <c r="B142" t="n">
-        <v>23.73277282714844</v>
+        <v>23.71375274658203</v>
       </c>
       <c r="C142" t="n">
         <v>33.16999816894531</v>
@@ -3955,11 +3967,11 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="1" t="n">
+      <c r="A143" s="2" t="n">
         <v>43039</v>
       </c>
       <c r="B143" t="n">
-        <v>26.45162773132324</v>
+        <v>26.43043899536133</v>
       </c>
       <c r="C143" t="n">
         <v>36.97000122070312</v>
@@ -3984,11 +3996,11 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="1" t="n">
+      <c r="A144" s="2" t="n">
         <v>43069</v>
       </c>
       <c r="B144" t="n">
-        <v>27.58925437927246</v>
+        <v>27.56715393066406</v>
       </c>
       <c r="C144" t="n">
         <v>38.56000137329102</v>
@@ -4013,11 +4025,11 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="1" t="n">
+      <c r="A145" s="2" t="n">
         <v>43100</v>
       </c>
       <c r="B145" t="n">
-        <v>30.38129043579102</v>
+        <v>30.35694694519043</v>
       </c>
       <c r="C145" t="n">
         <v>41.84000015258789</v>
@@ -4042,11 +4054,11 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="1" t="n">
+      <c r="A146" s="2" t="n">
         <v>43131</v>
       </c>
       <c r="B146" t="n">
-        <v>40.08237838745117</v>
+        <v>40.05027770996094</v>
       </c>
       <c r="C146" t="n">
         <v>55.20000076293945</v>
@@ -4071,11 +4083,11 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="1" t="n">
+      <c r="A147" s="2" t="n">
         <v>43159</v>
       </c>
       <c r="B147" t="n">
-        <v>38.77533340454102</v>
+        <v>38.74428558349609</v>
       </c>
       <c r="C147" t="n">
         <v>53.40000152587891</v>
@@ -4100,11 +4112,11 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="1" t="n">
+      <c r="A148" s="2" t="n">
         <v>43190</v>
       </c>
       <c r="B148" t="n">
-        <v>42.94102478027344</v>
+        <v>42.9066276550293</v>
       </c>
       <c r="C148" t="n">
         <v>58.52000045776367</v>
@@ -4129,11 +4141,11 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="1" t="n">
+      <c r="A149" s="2" t="n">
         <v>43220</v>
       </c>
       <c r="B149" t="n">
-        <v>42.47873687744141</v>
+        <v>42.44471740722656</v>
       </c>
       <c r="C149" t="n">
         <v>57.88999938964844</v>
@@ -4158,11 +4170,11 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="1" t="n">
+      <c r="A150" s="2" t="n">
         <v>43251</v>
       </c>
       <c r="B150" t="n">
-        <v>41.34870910644531</v>
+        <v>41.31558609008789</v>
       </c>
       <c r="C150" t="n">
         <v>56.34999847412109</v>
@@ -4187,11 +4199,11 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="1" t="n">
+      <c r="A151" s="2" t="n">
         <v>43281</v>
       </c>
       <c r="B151" t="n">
-        <v>41.8841438293457</v>
+        <v>41.85061264038086</v>
       </c>
       <c r="C151" t="n">
         <v>56.47000122070312</v>
@@ -4216,11 +4228,11 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="1" t="n">
+      <c r="A152" s="2" t="n">
         <v>43312</v>
       </c>
       <c r="B152" t="n">
-        <v>39.02858352661133</v>
+        <v>38.99732208251953</v>
       </c>
       <c r="C152" t="n">
         <v>52.61999893188477</v>
@@ -4245,11 +4257,11 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="1" t="n">
+      <c r="A153" s="2" t="n">
         <v>43343</v>
       </c>
       <c r="B153" t="n">
-        <v>39.71096038818359</v>
+        <v>39.67914581298828</v>
       </c>
       <c r="C153" t="n">
         <v>53.54000091552734</v>
@@ -4274,11 +4286,11 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="1" t="n">
+      <c r="A154" s="2" t="n">
         <v>43373</v>
       </c>
       <c r="B154" t="n">
-        <v>35.58746337890625</v>
+        <v>35.5589599609375</v>
       </c>
       <c r="C154" t="n">
         <v>47.34999847412109</v>
@@ -4303,11 +4315,11 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="1" t="n">
+      <c r="A155" s="2" t="n">
         <v>43404</v>
       </c>
       <c r="B155" t="n">
-        <v>30.23618698120117</v>
+        <v>30.21197509765625</v>
       </c>
       <c r="C155" t="n">
         <v>40.22999954223633</v>
@@ -4332,11 +4344,11 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="1" t="n">
+      <c r="A156" s="2" t="n">
         <v>43434</v>
       </c>
       <c r="B156" t="n">
-        <v>32.38571166992188</v>
+        <v>32.35977935791016</v>
       </c>
       <c r="C156" t="n">
         <v>43.09000015258789</v>
@@ -4361,11 +4373,11 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="1" t="n">
+      <c r="A157" s="2" t="n">
         <v>43465</v>
       </c>
       <c r="B157" t="n">
-        <v>29.50012588500977</v>
+        <v>29.47649192810059</v>
       </c>
       <c r="C157" t="n">
         <v>38.59000015258789</v>
@@ -4390,11 +4402,11 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="1" t="n">
+      <c r="A158" s="2" t="n">
         <v>43496</v>
       </c>
       <c r="B158" t="n">
-        <v>33.84983825683594</v>
+        <v>33.82271957397461</v>
       </c>
       <c r="C158" t="n">
         <v>44.27999877929688</v>
@@ -4419,11 +4431,11 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="1" t="n">
+      <c r="A159" s="2" t="n">
         <v>43524</v>
       </c>
       <c r="B159" t="n">
-        <v>35.59279251098633</v>
+        <v>35.56428146362305</v>
       </c>
       <c r="C159" t="n">
         <v>46.56000137329102</v>
@@ -4448,11 +4460,11 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="1" t="n">
+      <c r="A160" s="2" t="n">
         <v>43555</v>
       </c>
       <c r="B160" t="n">
-        <v>37.09475708007812</v>
+        <v>37.06504821777344</v>
       </c>
       <c r="C160" t="n">
         <v>47.88999938964844</v>
@@ -4477,11 +4489,11 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="1" t="n">
+      <c r="A161" s="2" t="n">
         <v>43585</v>
       </c>
       <c r="B161" t="n">
-        <v>37.42782974243164</v>
+        <v>37.39786148071289</v>
       </c>
       <c r="C161" t="n">
         <v>48.31999969482422</v>
@@ -4506,11 +4518,11 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="1" t="n">
+      <c r="A162" s="2" t="n">
         <v>43616</v>
       </c>
       <c r="B162" t="n">
-        <v>32.4162712097168</v>
+        <v>32.39031600952148</v>
       </c>
       <c r="C162" t="n">
         <v>41.84999847412109</v>
@@ -4535,11 +4547,11 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="1" t="n">
+      <c r="A163" s="2" t="n">
         <v>43646</v>
       </c>
       <c r="B163" t="n">
-        <v>37.02415084838867</v>
+        <v>36.99448776245117</v>
       </c>
       <c r="C163" t="n">
         <v>47.11999893188477</v>
@@ -4564,11 +4576,11 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="1" t="n">
+      <c r="A164" s="2" t="n">
         <v>43677</v>
       </c>
       <c r="B164" t="n">
-        <v>36.38769149780273</v>
+        <v>36.35855102539062</v>
       </c>
       <c r="C164" t="n">
         <v>46.31000137329102</v>
@@ -4593,11 +4605,11 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="1" t="n">
+      <c r="A165" s="2" t="n">
         <v>43708</v>
       </c>
       <c r="B165" t="n">
-        <v>39.45207977294922</v>
+        <v>39.42049026489258</v>
       </c>
       <c r="C165" t="n">
         <v>50.20999908447266</v>
@@ -4622,11 +4634,11 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="1" t="n">
+      <c r="A166" s="2" t="n">
         <v>43738</v>
       </c>
       <c r="B166" t="n">
-        <v>42.77591705322266</v>
+        <v>42.74166488647461</v>
       </c>
       <c r="C166" t="n">
         <v>53.79000091552734</v>
@@ -4651,11 +4663,11 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="1" t="n">
+      <c r="A167" s="2" t="n">
         <v>43769</v>
       </c>
       <c r="B167" t="n">
-        <v>46.14773178100586</v>
+        <v>46.11077117919922</v>
       </c>
       <c r="C167" t="n">
         <v>58.02999877929688</v>
@@ -4680,11 +4692,11 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="1" t="n">
+      <c r="A168" s="2" t="n">
         <v>43799</v>
       </c>
       <c r="B168" t="n">
-        <v>47.45987701416016</v>
+        <v>47.42187881469727</v>
       </c>
       <c r="C168" t="n">
         <v>59.68000030517578</v>
@@ -4709,11 +4721,11 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="1" t="n">
+      <c r="A169" s="2" t="n">
         <v>43830</v>
       </c>
       <c r="B169" t="n">
-        <v>47.83173751831055</v>
+        <v>47.79343032836914</v>
       </c>
       <c r="C169" t="n">
         <v>59.5</v>
@@ -4738,11 +4750,11 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="1" t="n">
+      <c r="A170" s="2" t="n">
         <v>43861</v>
       </c>
       <c r="B170" t="n">
-        <v>45.81395721435547</v>
+        <v>45.77727127075195</v>
       </c>
       <c r="C170" t="n">
         <v>56.9900016784668</v>
@@ -4767,11 +4779,11 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="1" t="n">
+      <c r="A171" s="2" t="n">
         <v>43890</v>
       </c>
       <c r="B171" t="n">
-        <v>38.54676055908203</v>
+        <v>38.51589202880859</v>
       </c>
       <c r="C171" t="n">
         <v>47.95000076293945</v>
@@ -4796,11 +4808,11 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="1" t="n">
+      <c r="A172" s="2" t="n">
         <v>43921</v>
       </c>
       <c r="B172" t="n">
-        <v>39.86548614501953</v>
+        <v>39.83355712890625</v>
       </c>
       <c r="C172" t="n">
         <v>48.79999923706055</v>
@@ -4825,11 +4837,11 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="1" t="n">
+      <c r="A173" s="2" t="n">
         <v>43951</v>
       </c>
       <c r="B173" t="n">
-        <v>40.804931640625</v>
+        <v>40.77225494384766</v>
       </c>
       <c r="C173" t="n">
         <v>49.95000076293945</v>
@@ -4854,11 +4866,11 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="1" t="n">
+      <c r="A174" s="2" t="n">
         <v>43982</v>
       </c>
       <c r="B174" t="n">
-        <v>43.32920074462891</v>
+        <v>43.29450225830078</v>
       </c>
       <c r="C174" t="n">
         <v>53.04000091552734</v>
@@ -4883,11 +4895,11 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="1" t="n">
+      <c r="A175" s="2" t="n">
         <v>44012</v>
       </c>
       <c r="B175" t="n">
-        <v>40.05833053588867</v>
+        <v>40.0262451171875</v>
       </c>
       <c r="C175" t="n">
         <v>48.40999984741211</v>
@@ -4912,11 +4924,11 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="1" t="n">
+      <c r="A176" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="B176" t="n">
-        <v>37.41867828369141</v>
+        <v>37.38870620727539</v>
       </c>
       <c r="C176" t="n">
         <v>45.22000122070312</v>
@@ -4941,11 +4953,11 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="1" t="n">
+      <c r="A177" s="2" t="n">
         <v>44074</v>
       </c>
       <c r="B177" t="n">
-        <v>39.71079254150391</v>
+        <v>39.67898941040039</v>
       </c>
       <c r="C177" t="n">
         <v>47.9900016784668</v>
@@ -4970,11 +4982,11 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="1" t="n">
+      <c r="A178" s="2" t="n">
         <v>44104</v>
       </c>
       <c r="B178" t="n">
-        <v>41.32692718505859</v>
+        <v>41.29384231567383</v>
       </c>
       <c r="C178" t="n">
         <v>49.27000045776367</v>
@@ -4999,11 +5011,11 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="1" t="n">
+      <c r="A179" s="2" t="n">
         <v>44135</v>
       </c>
       <c r="B179" t="n">
-        <v>40.11070251464844</v>
+        <v>40.07857131958008</v>
       </c>
       <c r="C179" t="n">
         <v>47.81999969482422</v>
@@ -5028,11 +5040,11 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="1" t="n">
+      <c r="A180" s="2" t="n">
         <v>44165</v>
       </c>
       <c r="B180" t="n">
-        <v>49.32894515991211</v>
+        <v>49.2894401550293</v>
       </c>
       <c r="C180" t="n">
         <v>58.81000137329102</v>
@@ -5057,11 +5069,11 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="1" t="n">
+      <c r="A181" s="2" t="n">
         <v>44196</v>
       </c>
       <c r="B181" t="n">
-        <v>52.68148803710938</v>
+        <v>52.63928985595703</v>
       </c>
       <c r="C181" t="n">
         <v>62.15999984741211</v>
@@ -5086,11 +5098,11 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="1" t="n">
+      <c r="A182" s="2" t="n">
         <v>44227</v>
       </c>
       <c r="B182" t="n">
-        <v>56.03763580322266</v>
+        <v>55.99276351928711</v>
       </c>
       <c r="C182" t="n">
         <v>66.12000274658203</v>
@@ -5115,11 +5127,11 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="1" t="n">
+      <c r="A183" s="2" t="n">
         <v>44255</v>
       </c>
       <c r="B183" t="n">
-        <v>62.06347274780273</v>
+        <v>62.01375579833984</v>
       </c>
       <c r="C183" t="n">
         <v>73.23000335693359</v>
@@ -5144,11 +5156,11 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="1" t="n">
+      <c r="A184" s="2" t="n">
         <v>44286</v>
       </c>
       <c r="B184" t="n">
-        <v>65.62571716308594</v>
+        <v>65.57312774658203</v>
       </c>
       <c r="C184" t="n">
         <v>76.75</v>
@@ -5173,11 +5185,11 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="1" t="n">
+      <c r="A185" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="B185" t="n">
-        <v>79.38359832763672</v>
+        <v>79.32000732421875</v>
       </c>
       <c r="C185" t="n">
         <v>92.83999633789062</v>
@@ -5202,11 +5214,11 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="1" t="n">
+      <c r="A186" s="2" t="n">
         <v>44347</v>
       </c>
       <c r="B186" t="n">
-        <v>82.48594665527344</v>
+        <v>82.41987609863281</v>
       </c>
       <c r="C186" t="n">
         <v>95.75</v>
@@ -5231,11 +5243,11 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="1" t="n">
+      <c r="A187" s="2" t="n">
         <v>44377</v>
       </c>
       <c r="B187" t="n">
-        <v>75.74923706054688</v>
+        <v>75.68856811523438</v>
       </c>
       <c r="C187" t="n">
         <v>87.93000030517578</v>
@@ -5260,11 +5272,11 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="1" t="n">
+      <c r="A188" s="2" t="n">
         <v>44408</v>
       </c>
       <c r="B188" t="n">
-        <v>75.72339630126953</v>
+        <v>75.66273498535156</v>
       </c>
       <c r="C188" t="n">
         <v>87.90000152587891</v>
@@ -5289,11 +5301,11 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="1" t="n">
+      <c r="A189" s="2" t="n">
         <v>44439</v>
       </c>
       <c r="B189" t="n">
-        <v>75.45632171630859</v>
+        <v>75.39590454101562</v>
       </c>
       <c r="C189" t="n">
         <v>87.58999633789062</v>
@@ -5318,11 +5330,11 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="1" t="n">
+      <c r="A190" s="2" t="n">
         <v>44469</v>
       </c>
       <c r="B190" t="n">
-        <v>71.66754150390625</v>
+        <v>71.61013793945312</v>
       </c>
       <c r="C190" t="n">
         <v>82.51999664306641</v>
@@ -5347,11 +5359,11 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="1" t="n">
+      <c r="A191" s="2" t="n">
         <v>44500</v>
       </c>
       <c r="B191" t="n">
-        <v>77.35614013671875</v>
+        <v>77.29417419433594</v>
       </c>
       <c r="C191" t="n">
         <v>89.06999969482422</v>
@@ -5376,11 +5388,11 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="1" t="n">
+      <c r="A192" s="2" t="n">
         <v>44530</v>
       </c>
       <c r="B192" t="n">
-        <v>89.16757965087891</v>
+        <v>89.09613037109375</v>
       </c>
       <c r="C192" t="n">
         <v>102.6699981689453</v>
@@ -5405,11 +5417,11 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="1" t="n">
+      <c r="A193" s="2" t="n">
         <v>44561</v>
       </c>
       <c r="B193" t="n">
-        <v>98.77938079833984</v>
+        <v>98.70025634765625</v>
       </c>
       <c r="C193" t="n">
         <v>112.9800033569336</v>
@@ -5434,11 +5446,11 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="1" t="n">
+      <c r="A194" s="2" t="n">
         <v>44592</v>
       </c>
       <c r="B194" t="n">
-        <v>93.68215179443359</v>
+        <v>93.60710906982422</v>
       </c>
       <c r="C194" t="n">
         <v>107.1500015258789</v>
@@ -5463,11 +5475,11 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="1" t="n">
+      <c r="A195" s="2" t="n">
         <v>44620</v>
       </c>
       <c r="B195" t="n">
-        <v>90.19365692138672</v>
+        <v>90.12142181396484</v>
       </c>
       <c r="C195" t="n">
         <v>103.1600036621094</v>
@@ -5492,11 +5504,11 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="1" t="n">
+      <c r="A196" s="2" t="n">
         <v>44651</v>
       </c>
       <c r="B196" t="n">
-        <v>79.18804168701172</v>
+        <v>79.12460327148438</v>
       </c>
       <c r="C196" t="n">
         <v>89.90000152587891</v>
@@ -5521,11 +5533,11 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="1" t="n">
+      <c r="A197" s="2" t="n">
         <v>44681</v>
       </c>
       <c r="B197" t="n">
-        <v>72.26457214355469</v>
+        <v>72.20670318603516</v>
       </c>
       <c r="C197" t="n">
         <v>82.04000091552734</v>
@@ -5550,11 +5562,11 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="1" t="n">
+      <c r="A198" s="2" t="n">
         <v>44712</v>
       </c>
       <c r="B198" t="n">
-        <v>74.58120727539062</v>
+        <v>74.52145385742188</v>
       </c>
       <c r="C198" t="n">
         <v>84.66999816894531</v>
@@ -5579,11 +5591,11 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="1" t="n">
+      <c r="A199" s="2" t="n">
         <v>44742</v>
       </c>
       <c r="B199" t="n">
-        <v>63.54891204833984</v>
+        <v>63.49800491333008</v>
       </c>
       <c r="C199" t="n">
         <v>71.44000244140625</v>
@@ -5608,11 +5620,11 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="1" t="n">
+      <c r="A200" s="2" t="n">
         <v>44773</v>
       </c>
       <c r="B200" t="n">
-        <v>71.14559936523438</v>
+        <v>71.08861541748047</v>
       </c>
       <c r="C200" t="n">
         <v>79.98000335693359</v>
@@ -5637,11 +5649,11 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="1" t="n">
+      <c r="A201" s="2" t="n">
         <v>44804</v>
       </c>
       <c r="B201" t="n">
-        <v>59.56375885009766</v>
+        <v>59.51604461669922</v>
       </c>
       <c r="C201" t="n">
         <v>66.95999908447266</v>
@@ -5666,11 +5678,11 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="1" t="n">
+      <c r="A202" s="2" t="n">
         <v>44834</v>
       </c>
       <c r="B202" t="n">
-        <v>47.89087295532227</v>
+        <v>47.85250854492188</v>
       </c>
       <c r="C202" t="n">
         <v>53.22999954223633</v>
@@ -5695,11 +5707,11 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="1" t="n">
+      <c r="A203" s="2" t="n">
         <v>44865</v>
       </c>
       <c r="B203" t="n">
-        <v>44.678955078125</v>
+        <v>44.64316940307617</v>
       </c>
       <c r="C203" t="n">
         <v>49.65999984741211</v>
@@ -5724,11 +5736,11 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="1" t="n">
+      <c r="A204" s="2" t="n">
         <v>44895</v>
       </c>
       <c r="B204" t="n">
-        <v>47.65694808959961</v>
+        <v>47.61877059936523</v>
       </c>
       <c r="C204" t="n">
         <v>52.97000122070312</v>
@@ -5753,11 +5765,11 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="1" t="n">
+      <c r="A205" s="2" t="n">
         <v>44926</v>
       </c>
       <c r="B205" t="n">
-        <v>47.99190139770508</v>
+        <v>47.95346832275391</v>
       </c>
       <c r="C205" t="n">
         <v>52.61000061035156</v>
@@ -5782,11 +5794,11 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="1" t="n">
+      <c r="A206" s="2" t="n">
         <v>44957</v>
       </c>
       <c r="B206" t="n">
-        <v>61.83028793334961</v>
+        <v>61.78076553344727</v>
       </c>
       <c r="C206" t="n">
         <v>67.77999877929688</v>
@@ -5811,11 +5823,11 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="1" t="n">
+      <c r="A207" s="2" t="n">
         <v>44985</v>
       </c>
       <c r="B207" t="n">
-        <v>58.89292526245117</v>
+        <v>58.84576034545898</v>
       </c>
       <c r="C207" t="n">
         <v>64.55999755859375</v>
@@ -5840,11 +5852,11 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="1" t="n">
+      <c r="A208" s="2" t="n">
         <v>45016</v>
       </c>
       <c r="B208" t="n">
-        <v>61.00407791137695</v>
+        <v>60.95523071289062</v>
       </c>
       <c r="C208" t="n">
         <v>66.12000274658203</v>
@@ -5869,11 +5881,11 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="1" t="n">
+      <c r="A209" s="2" t="n">
         <v>45046</v>
       </c>
       <c r="B209" t="n">
-        <v>54.2227783203125</v>
+        <v>54.17934417724609</v>
       </c>
       <c r="C209" t="n">
         <v>58.77000045776367</v>
@@ -5896,11 +5908,11 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="1" t="n">
+      <c r="A210" s="2" t="n">
         <v>45077</v>
       </c>
       <c r="B210" t="n">
-        <v>55.44986343383789</v>
+        <v>55.40545654296875</v>
       </c>
       <c r="C210" t="n">
         <v>60.09999847412109</v>
@@ -5923,11 +5935,11 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="1" t="n">
+      <c r="A211" s="2" t="n">
         <v>45107</v>
       </c>
       <c r="B211" t="n">
-        <v>57.71118927001953</v>
+        <v>57.66496658325195</v>
       </c>
       <c r="C211" t="n">
         <v>61.86999893188477</v>
@@ -5950,11 +5962,11 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="1" t="n">
+      <c r="A212" s="2" t="n">
         <v>45138</v>
       </c>
       <c r="B212" t="n">
-        <v>59.23162460327148</v>
+        <v>59.18418502807617</v>
       </c>
       <c r="C212" t="n">
         <v>63.5</v>
@@ -5977,11 +5989,11 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="1" t="n">
+      <c r="A213" s="2" t="n">
         <v>45169</v>
       </c>
       <c r="B213" t="n">
-        <v>66.03159332275391</v>
+        <v>65.97870635986328</v>
       </c>
       <c r="C213" t="n">
         <v>70.79000091552734</v>
@@ -6004,11 +6016,11 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="1" t="n">
+      <c r="A214" s="2" t="n">
         <v>45199</v>
       </c>
       <c r="B214" t="n">
-        <v>62.17739868164062</v>
+        <v>62.12759399414062</v>
       </c>
       <c r="C214" t="n">
         <v>65.94999694824219</v>
@@ -6031,11 +6043,11 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="1" t="n">
+      <c r="A215" s="2" t="n">
         <v>45230</v>
       </c>
       <c r="B215" t="n">
-        <v>64.34584045410156</v>
+        <v>64.29428100585938</v>
       </c>
       <c r="C215" t="n">
         <v>68.25</v>
@@ -6058,11 +6070,11 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="1" t="n">
+      <c r="A216" s="2" t="n">
         <v>45260</v>
       </c>
       <c r="B216" t="n">
-        <v>74.57516479492188</v>
+        <v>74.51542663574219</v>
       </c>
       <c r="C216" t="n">
         <v>79.09999847412109</v>
@@ -6085,11 +6097,11 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="1" t="n">
+      <c r="A217" s="2" t="n">
         <v>45291</v>
       </c>
       <c r="B217" t="n">
-        <v>81.16366577148438</v>
+        <v>81.09866333007812</v>
       </c>
       <c r="C217" t="n">
         <v>85.37000274658203</v>
@@ -6112,11 +6124,11 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="1" t="n">
+      <c r="A218" s="2" t="n">
         <v>45322</v>
       </c>
       <c r="B218" t="n">
-        <v>81.45839691162109</v>
+        <v>81.39314270019531</v>
       </c>
       <c r="C218" t="n">
         <v>85.68000030517578</v>
@@ -6139,11 +6151,11 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="1" t="n">
+      <c r="A219" s="2" t="n">
         <v>45351</v>
       </c>
       <c r="B219" t="n">
-        <v>88.46526336669922</v>
+        <v>88.39440155029297</v>
       </c>
       <c r="C219" t="n">
         <v>93.05000305175781</v>
@@ -6166,11 +6178,11 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="1" t="n">
+      <c r="A220" s="2" t="n">
         <v>45382</v>
       </c>
       <c r="B220" t="n">
-        <v>89.18642425537109</v>
+        <v>89.11498260498047</v>
       </c>
       <c r="C220" t="n">
         <v>93.05000305175781</v>
@@ -6193,11 +6205,11 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="1" t="n">
+      <c r="A221" s="2" t="n">
         <v>45412</v>
       </c>
       <c r="B221" t="n">
-        <v>82.34288024902344</v>
+        <v>82.27693176269531</v>
       </c>
       <c r="C221" t="n">
         <v>85.91000366210938</v>
@@ -6220,11 +6232,11 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="1" t="n">
+      <c r="A222" s="2" t="n">
         <v>45443</v>
       </c>
       <c r="B222" t="n">
-        <v>89.3685302734375</v>
+        <v>89.29694366455078</v>
       </c>
       <c r="C222" t="n">
         <v>93.23999786376953</v>
@@ -6247,11 +6259,11 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="1" t="n">
+      <c r="A223" s="2" t="n">
         <v>45473</v>
       </c>
       <c r="B223" t="n">
-        <v>99.64012145996094</v>
+        <v>99.56031799316406</v>
       </c>
       <c r="C223" t="n">
         <v>103.2699966430664</v>
@@ -6274,11 +6286,11 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="1" t="n">
+      <c r="A224" s="2" t="n">
         <v>45504</v>
       </c>
       <c r="B224" t="n">
-        <v>98.57878875732422</v>
+        <v>98.49983215332031</v>
       </c>
       <c r="C224" t="n">
         <v>102.1699981689453</v>
@@ -6301,11 +6313,11 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="1" t="n">
+      <c r="A225" s="2" t="n">
         <v>45535</v>
       </c>
       <c r="B225" t="n">
-        <v>96.05088043212891</v>
+        <v>95.97395324707031</v>
       </c>
       <c r="C225" t="n">
         <v>99.55000305175781</v>
@@ -6330,11 +6342,11 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="1" t="n">
+      <c r="A226" s="2" t="n">
         <v>45565</v>
       </c>
       <c r="B226" t="n">
-        <v>106.3911209106445</v>
+        <v>106.3059158325195</v>
       </c>
       <c r="C226" t="n">
         <v>109.5299987792969</v>
@@ -6359,11 +6371,11 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="1" t="n">
+      <c r="A227" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="B227" t="n">
-        <v>97.49362945556641</v>
+        <v>97.41554260253906</v>
       </c>
       <c r="C227" t="n">
         <v>100.370002746582</v>
@@ -6388,11 +6400,11 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="1" t="n">
+      <c r="A228" s="2" t="n">
         <v>45626</v>
       </c>
       <c r="B228" t="n">
-        <v>98.42612457275391</v>
+        <v>98.3472900390625</v>
       </c>
       <c r="C228" t="n">
         <v>101.3300018310547</v>
@@ -6417,11 +6429,11 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="1" t="n">
+      <c r="A229" s="2" t="n">
         <v>45657</v>
       </c>
       <c r="B229" t="n">
-        <v>84.45935821533203</v>
+        <v>84.39170837402344</v>
       </c>
       <c r="C229" t="n">
         <v>86.30999755859375</v>
@@ -6446,11 +6458,11 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="1" t="n">
+      <c r="A230" s="2" t="n">
         <v>45688</v>
       </c>
       <c r="B230" t="n">
-        <v>94.29388427734375</v>
+        <v>94.21836090087891</v>
       </c>
       <c r="C230" t="n">
         <v>96.36000061035156</v>
@@ -6475,11 +6487,11 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="1" t="n">
+      <c r="A231" s="2" t="n">
         <v>45716</v>
       </c>
       <c r="B231" t="n">
-        <v>99.72488403320312</v>
+        <v>99.64500427246094</v>
       </c>
       <c r="C231" t="n">
         <v>101.9100036621094</v>
@@ -6504,11 +6516,11 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="1" t="n">
+      <c r="A232" s="2" t="n">
         <v>45747</v>
       </c>
       <c r="B232" t="n">
-        <v>83.80928039550781</v>
+        <v>83.74215698242188</v>
       </c>
       <c r="C232" t="n">
         <v>84.94999694824219</v>
@@ -6533,11 +6545,11 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="1" t="n">
+      <c r="A233" s="2" t="n">
         <v>45777</v>
       </c>
       <c r="B233" t="n">
-        <v>89.80765533447266</v>
+        <v>89.73571014404297</v>
       </c>
       <c r="C233" t="n">
         <v>91.02999877929688</v>
@@ -6562,11 +6574,11 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="1" t="n">
+      <c r="A234" s="2" t="n">
         <v>45808</v>
       </c>
       <c r="B234" t="n">
-        <v>116.3563003540039</v>
+        <v>116.2631072998047</v>
       </c>
       <c r="C234" t="n">
         <v>117.9400024414062</v>
@@ -6591,11 +6603,11 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="1" t="n">
+      <c r="A235" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="B235" t="n">
-        <v>143.1480712890625</v>
+        <v>143.0334014892578</v>
       </c>
       <c r="C235" t="n">
         <v>144.3300018310547</v>
@@ -6620,11 +6632,11 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="1" t="n">
+      <c r="A236" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="B236" t="n">
-        <v>155.7242126464844</v>
+        <v>155.5994873046875</v>
       </c>
       <c r="C236" t="n">
         <v>157.0099945068359</v>
@@ -6649,11 +6661,11 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="1" t="n">
+      <c r="A237" s="2" t="n">
         <v>45900</v>
       </c>
       <c r="B237" t="n">
-        <v>166.0291290283203</v>
+        <v>165.8961486816406</v>
       </c>
       <c r="C237" t="n">
         <v>167.3999938964844</v>
@@ -6678,11 +6690,11 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="1" t="n">
+      <c r="A238" s="2" t="n">
         <v>45930</v>
       </c>
       <c r="B238" t="n">
-        <v>234.8648376464844</v>
+        <v>234.6767272949219</v>
       </c>
       <c r="C238" t="n">
         <v>236.0599975585938</v>
@@ -6707,11 +6719,11 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="1" t="n">
+      <c r="A239" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="B239" t="n">
-        <v>254.5845184326172</v>
+        <v>254.3805999755859</v>
       </c>
       <c r="C239" t="n">
         <v>255.8800048828125</v>
@@ -6736,11 +6748,11 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="1" t="n">
+      <c r="A240" s="2" t="n">
         <v>45991</v>
       </c>
       <c r="B240" t="n">
-        <v>275.2891235351562</v>
+        <v>275.0686645507812</v>
       </c>
       <c r="C240" t="n">
         <v>276.6900024414062</v>
@@ -6765,11 +6777,11 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="1" t="n">
+      <c r="A241" s="2" t="n">
         <v>46022</v>
       </c>
       <c r="B241" t="n">
-        <v>274.7145690917969</v>
+        <v>274.4945373535156</v>
       </c>
       <c r="C241" t="n">
         <v>275.3900146484375</v>
@@ -6794,11 +6806,11 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="1" t="n">
+      <c r="A242" s="2" t="n">
         <v>46053</v>
       </c>
       <c r="B242" t="n">
-        <v>406.6900939941406</v>
+        <v>406.3643493652344</v>
       </c>
       <c r="C242" t="n">
         <v>407.6900024414062</v>
@@ -6823,11 +6835,11 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="1" t="n">
+      <c r="A243" s="2" t="n">
         <v>46081</v>
       </c>
       <c r="B243" t="n">
-        <v>406.8396911621094</v>
+        <v>406.5138244628906</v>
       </c>
       <c r="C243" t="n">
         <v>407.8399963378906</v>
@@ -6852,11 +6864,11 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="1" t="n">
+      <c r="A244" s="2" t="n">
         <v>46112</v>
       </c>
       <c r="B244" t="n">
-        <v>391.4808654785156</v>
+        <v>391.1672973632812</v>
       </c>
       <c r="C244" t="n">
         <v>391.760009765625</v>
@@ -6881,11 +6893,11 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="1" t="n">
+      <c r="A245" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="B245" t="n">
-        <v>673.1600341796875</v>
+        <v>672.620849609375</v>
       </c>
       <c r="C245" t="n">
         <v>673.6400146484375</v>
@@ -6910,11 +6922,11 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="1" t="n">
+      <c r="A246" s="2" t="n">
         <v>46173</v>
       </c>
       <c r="B246" t="n">
-        <v>879.173095703125</v>
+        <v>878.4689331054688</v>
       </c>
       <c r="C246" t="n">
         <v>879.7999877929688</v>
@@ -6939,11 +6951,11 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="1" t="n">
+      <c r="A247" s="2" t="n">
         <v>46203</v>
       </c>
       <c r="B247" t="n">
-        <v>965</v>
+        <v>964.22705078125</v>
       </c>
       <c r="C247" t="n">
         <v>965</v>
@@ -6968,11 +6980,11 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="1" t="n">
+      <c r="A248" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="B248" t="n">
-        <v>856.1300048828125</v>
+        <v>855.4442749023438</v>
       </c>
       <c r="C248" t="n">
         <v>856.1300048828125</v>
@@ -6997,11 +7009,11 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="1" t="n">
+      <c r="A249" s="2" t="n">
         <v>46265</v>
       </c>
       <c r="B249" t="n">
-        <v>828.3800048828125</v>
+        <v>827.7164916992188</v>
       </c>
       <c r="C249" t="n">
         <v>828.3800048828125</v>
@@ -7026,32 +7038,32 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="1" t="n">
+      <c r="A250" s="2" t="n">
         <v>46295</v>
       </c>
       <c r="B250" t="n">
-        <v>923.8599853515625</v>
+        <v>905.9199829101562</v>
       </c>
       <c r="C250" t="n">
-        <v>923.8599853515625</v>
+        <v>905.9199829101562</v>
       </c>
       <c r="D250" t="n">
-        <v>62952500</v>
+        <v>66019600</v>
       </c>
       <c r="E250" t="n">
         <v>13.9</v>
       </c>
       <c r="F250" t="n">
-        <v>66.46474714759442</v>
+        <v>65.17409948993929</v>
       </c>
       <c r="G250" t="n">
         <v>226644518</v>
       </c>
       <c r="H250" t="n">
-        <v>209387801079.4919</v>
+        <v>205321797873.2406</v>
       </c>
       <c r="I250" t="n">
-        <v>0.2777587587624775</v>
+        <v>0.2912914046304001</v>
       </c>
     </row>
   </sheetData>
@@ -7083,75 +7095,75 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>start</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>eps_trimestral</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>origen</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>filed_ttm</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>39998</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>40088</v>
       </c>
-      <c r="C2" s="1" t="n">
+      <c r="C2" s="2" t="n">
         <v>40485</v>
       </c>
       <c r="D2" t="inlineStr">
@@ -7187,13 +7199,13 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>40089</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>40179</v>
       </c>
-      <c r="C3" s="1" t="n">
+      <c r="C3" s="2" t="n">
         <v>40577</v>
       </c>
       <c r="D3" t="inlineStr">
@@ -7229,13 +7241,13 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>40180</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>40270</v>
       </c>
-      <c r="C4" s="1" t="n">
+      <c r="C4" s="2" t="n">
         <v>40666</v>
       </c>
       <c r="D4" t="inlineStr">
@@ -7271,13 +7283,13 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>40271</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>40361</v>
       </c>
-      <c r="C5" s="1" t="n">
+      <c r="C5" s="2" t="n">
         <v>40772</v>
       </c>
       <c r="D5" t="inlineStr">
@@ -7304,7 +7316,7 @@
       <c r="I5" t="n">
         <v>3.140000000000001</v>
       </c>
-      <c r="J5" s="1" t="n">
+      <c r="J5" s="2" t="n">
         <v>40772</v>
       </c>
       <c r="K5" t="n">
@@ -7317,13 +7329,13 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>40362</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40452</v>
       </c>
-      <c r="C6" s="1" t="n">
+      <c r="C6" s="2" t="n">
         <v>40485</v>
       </c>
       <c r="D6" t="inlineStr">
@@ -7350,7 +7362,7 @@
       <c r="I6" t="n">
         <v>3.1</v>
       </c>
-      <c r="J6" s="1" t="n">
+      <c r="J6" s="2" t="n">
         <v>40772</v>
       </c>
       <c r="K6" t="n">
@@ -7363,13 +7375,13 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40453</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40543</v>
       </c>
-      <c r="C7" s="1" t="n">
+      <c r="C7" s="2" t="n">
         <v>40577</v>
       </c>
       <c r="D7" t="inlineStr">
@@ -7396,7 +7408,7 @@
       <c r="I7" t="n">
         <v>2.38</v>
       </c>
-      <c r="J7" s="1" t="n">
+      <c r="J7" s="2" t="n">
         <v>40772</v>
       </c>
       <c r="K7" t="n">
@@ -7409,13 +7421,13 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40544</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40634</v>
       </c>
-      <c r="C8" s="1" t="n">
+      <c r="C8" s="2" t="n">
         <v>40666</v>
       </c>
       <c r="D8" t="inlineStr">
@@ -7442,7 +7454,7 @@
       <c r="I8" t="n">
         <v>1.590000000000001</v>
       </c>
-      <c r="J8" s="1" t="n">
+      <c r="J8" s="2" t="n">
         <v>40772</v>
       </c>
       <c r="K8" t="n">
@@ -7455,13 +7467,13 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40635</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40725</v>
       </c>
-      <c r="C9" s="1" t="n">
+      <c r="C9" s="2" t="n">
         <v>40772</v>
       </c>
       <c r="D9" t="inlineStr">
@@ -7488,7 +7500,7 @@
       <c r="I9" t="n">
         <v>1.09</v>
       </c>
-      <c r="J9" s="1" t="n">
+      <c r="J9" s="2" t="n">
         <v>40772</v>
       </c>
       <c r="K9" t="n">
@@ -7501,13 +7513,13 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40726</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40816</v>
       </c>
-      <c r="C10" s="1" t="n">
+      <c r="C10" s="2" t="n">
         <v>40843</v>
       </c>
       <c r="D10" t="inlineStr">
@@ -7534,7 +7546,7 @@
       <c r="I10" t="n">
         <v>1.1</v>
       </c>
-      <c r="J10" s="1" t="n">
+      <c r="J10" s="2" t="n">
         <v>40843</v>
       </c>
       <c r="K10" t="n">
@@ -7547,13 +7559,13 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40817</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40907</v>
       </c>
-      <c r="C11" s="1" t="n">
+      <c r="C11" s="2" t="n">
         <v>40940</v>
       </c>
       <c r="D11" t="inlineStr">
@@ -7580,7 +7592,7 @@
       <c r="I11" t="n">
         <v>2.07</v>
       </c>
-      <c r="J11" s="1" t="n">
+      <c r="J11" s="2" t="n">
         <v>40940</v>
       </c>
       <c r="K11" t="n">
@@ -7593,13 +7605,13 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40909</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>40998</v>
       </c>
-      <c r="C12" s="1" t="n">
+      <c r="C12" s="2" t="n">
         <v>41029</v>
       </c>
       <c r="D12" t="inlineStr">
@@ -7626,7 +7638,7 @@
       <c r="I12" t="n">
         <v>4.340000000000001</v>
       </c>
-      <c r="J12" s="1" t="n">
+      <c r="J12" s="2" t="n">
         <v>41029</v>
       </c>
       <c r="K12" t="n">
@@ -7639,13 +7651,13 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>40999</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>41089</v>
       </c>
-      <c r="C13" s="1" t="n">
+      <c r="C13" s="2" t="n">
         <v>41130</v>
       </c>
       <c r="D13" t="inlineStr">
@@ -7672,7 +7684,7 @@
       <c r="I13" t="n">
         <v>6.490000000000001</v>
       </c>
-      <c r="J13" s="1" t="n">
+      <c r="J13" s="2" t="n">
         <v>41130</v>
       </c>
       <c r="K13" t="n">
@@ -7685,13 +7697,13 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>41090</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>41180</v>
       </c>
-      <c r="C14" s="1" t="n">
+      <c r="C14" s="2" t="n">
         <v>41213</v>
       </c>
       <c r="D14" t="inlineStr">
@@ -7718,7 +7730,7 @@
       <c r="I14" t="n">
         <v>7.590000000000001</v>
       </c>
-      <c r="J14" s="1" t="n">
+      <c r="J14" s="2" t="n">
         <v>41213</v>
       </c>
       <c r="K14" t="n">
@@ -7731,13 +7743,13 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>41181</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>41271</v>
       </c>
-      <c r="C15" s="1" t="n">
+      <c r="C15" s="2" t="n">
         <v>41303</v>
       </c>
       <c r="D15" t="inlineStr">
@@ -7764,7 +7776,7 @@
       <c r="I15" t="n">
         <v>7.61</v>
       </c>
-      <c r="J15" s="1" t="n">
+      <c r="J15" s="2" t="n">
         <v>41303</v>
       </c>
       <c r="K15" t="n">
@@ -7777,13 +7789,13 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>41272</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>41362</v>
       </c>
-      <c r="C16" s="1" t="n">
+      <c r="C16" s="2" t="n">
         <v>41396</v>
       </c>
       <c r="D16" t="inlineStr">
@@ -7810,7 +7822,7 @@
       <c r="I16" t="n">
         <v>6.260000000000001</v>
       </c>
-      <c r="J16" s="1" t="n">
+      <c r="J16" s="2" t="n">
         <v>41396</v>
       </c>
       <c r="K16" t="n">
@@ -7823,13 +7835,13 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41363</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41453</v>
       </c>
-      <c r="C17" s="1" t="n">
+      <c r="C17" s="2" t="n">
         <v>41494</v>
       </c>
       <c r="D17" t="inlineStr">
@@ -7856,7 +7868,7 @@
       <c r="I17" t="n">
         <v>4.81</v>
       </c>
-      <c r="J17" s="1" t="n">
+      <c r="J17" s="2" t="n">
         <v>41494</v>
       </c>
       <c r="K17" t="n">
@@ -7869,13 +7881,13 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41454</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41544</v>
       </c>
-      <c r="C18" s="1" t="n">
+      <c r="C18" s="2" t="n">
         <v>41576</v>
       </c>
       <c r="D18" t="inlineStr">
@@ -7902,7 +7914,7 @@
       <c r="I18" t="n">
         <v>4.550000000000001</v>
       </c>
-      <c r="J18" s="1" t="n">
+      <c r="J18" s="2" t="n">
         <v>41576</v>
       </c>
       <c r="K18" t="n">
@@ -7915,13 +7927,13 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41545</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41635</v>
       </c>
-      <c r="C19" s="1" t="n">
+      <c r="C19" s="2" t="n">
         <v>41667</v>
       </c>
       <c r="D19" t="inlineStr">
@@ -7948,7 +7960,7 @@
       <c r="I19" t="n">
         <v>4.490000000000001</v>
       </c>
-      <c r="J19" s="1" t="n">
+      <c r="J19" s="2" t="n">
         <v>41667</v>
       </c>
       <c r="K19" t="n">
@@ -7961,13 +7973,13 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41636</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41726</v>
       </c>
-      <c r="C20" s="1" t="n">
+      <c r="C20" s="2" t="n">
         <v>41759</v>
       </c>
       <c r="D20" t="inlineStr">
@@ -7994,7 +8006,7 @@
       <c r="I20" t="n">
         <v>4.530000000000001</v>
       </c>
-      <c r="J20" s="1" t="n">
+      <c r="J20" s="2" t="n">
         <v>41759</v>
       </c>
       <c r="K20" t="n">
@@ -8007,13 +8019,13 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41727</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41817</v>
       </c>
-      <c r="C21" s="1" t="n">
+      <c r="C21" s="2" t="n">
         <v>41859</v>
       </c>
       <c r="D21" t="inlineStr">
@@ -8040,7 +8052,7 @@
       <c r="I21" t="n">
         <v>4.52</v>
       </c>
-      <c r="J21" s="1" t="n">
+      <c r="J21" s="2" t="n">
         <v>41859</v>
       </c>
       <c r="K21" t="n">
@@ -8053,13 +8065,13 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41818</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41915</v>
       </c>
-      <c r="C22" s="1" t="n">
+      <c r="C22" s="2" t="n">
         <v>41946</v>
       </c>
       <c r="D22" t="inlineStr">
@@ -8086,7 +8098,7 @@
       <c r="I22" t="n">
         <v>4.49</v>
       </c>
-      <c r="J22" s="1" t="n">
+      <c r="J22" s="2" t="n">
         <v>41946</v>
       </c>
       <c r="K22" t="n">
@@ -8099,13 +8111,13 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>41916</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>42006</v>
       </c>
-      <c r="C23" s="1" t="n">
+      <c r="C23" s="2" t="n">
         <v>42034</v>
       </c>
       <c r="D23" t="inlineStr">
@@ -8132,7 +8144,7 @@
       <c r="I23" t="n">
         <v>6.03</v>
       </c>
-      <c r="J23" s="1" t="n">
+      <c r="J23" s="2" t="n">
         <v>42034</v>
       </c>
       <c r="K23" t="n">
@@ -8145,13 +8157,13 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>42007</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>42097</v>
       </c>
-      <c r="C24" s="1" t="n">
+      <c r="C24" s="2" t="n">
         <v>42124</v>
       </c>
       <c r="D24" t="inlineStr">
@@ -8178,7 +8190,7 @@
       <c r="I24" t="n">
         <v>5.74</v>
       </c>
-      <c r="J24" s="1" t="n">
+      <c r="J24" s="2" t="n">
         <v>42124</v>
       </c>
       <c r="K24" t="n">
@@ -8191,13 +8203,13 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>42098</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>42188</v>
       </c>
-      <c r="C25" s="1" t="n">
+      <c r="C25" s="2" t="n">
         <v>42228</v>
       </c>
       <c r="D25" t="inlineStr">
@@ -8224,7 +8236,7 @@
       <c r="I25" t="n">
         <v>5.260000000000001</v>
       </c>
-      <c r="J25" s="1" t="n">
+      <c r="J25" s="2" t="n">
         <v>42228</v>
       </c>
       <c r="K25" t="n">
@@ -8237,13 +8249,13 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>42189</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>42279</v>
       </c>
-      <c r="C26" s="1" t="n">
+      <c r="C26" s="2" t="n">
         <v>42307</v>
       </c>
       <c r="D26" t="inlineStr">
@@ -8270,7 +8282,7 @@
       <c r="I26" t="n">
         <v>4.240000000000001</v>
       </c>
-      <c r="J26" s="1" t="n">
+      <c r="J26" s="2" t="n">
         <v>42307</v>
       </c>
       <c r="K26" t="n">
@@ -8283,13 +8295,13 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>42280</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42370</v>
       </c>
-      <c r="C27" s="1" t="n">
+      <c r="C27" s="2" t="n">
         <v>42398</v>
       </c>
       <c r="D27" t="inlineStr">
@@ -8316,7 +8328,7 @@
       <c r="I27" t="n">
         <v>2.010000000000001</v>
       </c>
-      <c r="J27" s="1" t="n">
+      <c r="J27" s="2" t="n">
         <v>42398</v>
       </c>
       <c r="K27" t="n">
@@ -8329,13 +8341,13 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42371</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42461</v>
       </c>
-      <c r="C28" s="1" t="n">
+      <c r="C28" s="2" t="n">
         <v>42489</v>
       </c>
       <c r="D28" t="inlineStr">
@@ -8362,7 +8374,7 @@
       <c r="I28" t="n">
         <v>1.060000000000001</v>
       </c>
-      <c r="J28" s="1" t="n">
+      <c r="J28" s="2" t="n">
         <v>42489</v>
       </c>
       <c r="K28" t="n">
@@ -8375,13 +8387,13 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42462</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42552</v>
       </c>
-      <c r="C29" s="1" t="n">
+      <c r="C29" s="2" t="n">
         <v>42587</v>
       </c>
       <c r="D29" t="inlineStr">
@@ -8408,7 +8420,7 @@
       <c r="I29" t="n">
         <v>0.8200000000000007</v>
       </c>
-      <c r="J29" s="1" t="n">
+      <c r="J29" s="2" t="n">
         <v>42587</v>
       </c>
       <c r="K29" t="n">
@@ -8421,13 +8433,13 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42553</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42643</v>
       </c>
-      <c r="C30" s="1" t="n">
+      <c r="C30" s="2" t="n">
         <v>42671</v>
       </c>
       <c r="D30" t="inlineStr">
@@ -8454,7 +8466,7 @@
       <c r="I30" t="n">
         <v>1.260000000000001</v>
       </c>
-      <c r="J30" s="1" t="n">
+      <c r="J30" s="2" t="n">
         <v>42671</v>
       </c>
       <c r="K30" t="n">
@@ -8467,13 +8479,13 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42644</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42734</v>
       </c>
-      <c r="C31" s="1" t="n">
+      <c r="C31" s="2" t="n">
         <v>42761</v>
       </c>
       <c r="D31" t="inlineStr">
@@ -8500,7 +8512,7 @@
       <c r="I31" t="n">
         <v>1.710000000000001</v>
       </c>
-      <c r="J31" s="1" t="n">
+      <c r="J31" s="2" t="n">
         <v>42761</v>
       </c>
       <c r="K31" t="n">
@@ -8513,13 +8525,13 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42735</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42825</v>
       </c>
-      <c r="C32" s="1" t="n">
+      <c r="C32" s="2" t="n">
         <v>42853</v>
       </c>
       <c r="D32" t="inlineStr">
@@ -8546,7 +8558,7 @@
       <c r="I32" t="n">
         <v>2.430000000000001</v>
       </c>
-      <c r="J32" s="1" t="n">
+      <c r="J32" s="2" t="n">
         <v>42853</v>
       </c>
       <c r="K32" t="n">
@@ -8559,13 +8571,13 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42826</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42916</v>
       </c>
-      <c r="C33" s="1" t="n">
+      <c r="C33" s="2" t="n">
         <v>42951</v>
       </c>
       <c r="D33" t="inlineStr">
@@ -8592,7 +8604,7 @@
       <c r="I33" t="n">
         <v>2.580000000000001</v>
       </c>
-      <c r="J33" s="1" t="n">
+      <c r="J33" s="2" t="n">
         <v>42951</v>
       </c>
       <c r="K33" t="n">
@@ -8605,13 +8617,13 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42917</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>43007</v>
       </c>
-      <c r="C34" s="1" t="n">
+      <c r="C34" s="2" t="n">
         <v>43035</v>
       </c>
       <c r="D34" t="inlineStr">
@@ -8638,7 +8650,7 @@
       <c r="I34" t="n">
         <v>2.65</v>
       </c>
-      <c r="J34" s="1" t="n">
+      <c r="J34" s="2" t="n">
         <v>43035</v>
       </c>
       <c r="K34" t="n">
@@ -8651,13 +8663,13 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>43008</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>43098</v>
       </c>
-      <c r="C35" s="1" t="n">
+      <c r="C35" s="2" t="n">
         <v>43129</v>
       </c>
       <c r="D35" t="inlineStr">
@@ -8684,7 +8696,7 @@
       <c r="I35" t="n">
         <v>2.200000000000001</v>
       </c>
-      <c r="J35" s="1" t="n">
+      <c r="J35" s="2" t="n">
         <v>43129</v>
       </c>
       <c r="K35" t="n">
@@ -8697,13 +8709,13 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>43099</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>43189</v>
       </c>
-      <c r="C36" s="1" t="n">
+      <c r="C36" s="2" t="n">
         <v>43221</v>
       </c>
       <c r="D36" t="inlineStr">
@@ -8730,7 +8742,7 @@
       <c r="I36" t="n">
         <v>2.860000000000001</v>
       </c>
-      <c r="J36" s="1" t="n">
+      <c r="J36" s="2" t="n">
         <v>43221</v>
       </c>
       <c r="K36" t="n">
@@ -8743,13 +8755,13 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>43190</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>43280</v>
       </c>
-      <c r="C37" s="1" t="n">
+      <c r="C37" s="2" t="n">
         <v>43315</v>
       </c>
       <c r="D37" t="inlineStr">
@@ -8776,7 +8788,7 @@
       <c r="I37" t="n">
         <v>4.050000000000001</v>
       </c>
-      <c r="J37" s="1" t="n">
+      <c r="J37" s="2" t="n">
         <v>43315</v>
       </c>
       <c r="K37" t="n">
@@ -8789,13 +8801,13 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>43281</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43371</v>
       </c>
-      <c r="C38" s="1" t="n">
+      <c r="C38" s="2" t="n">
         <v>43406</v>
       </c>
       <c r="D38" t="inlineStr">
@@ -8822,7 +8834,7 @@
       <c r="I38" t="n">
         <v>4.970000000000001</v>
       </c>
-      <c r="J38" s="1" t="n">
+      <c r="J38" s="2" t="n">
         <v>43406</v>
       </c>
       <c r="K38" t="n">
@@ -8835,13 +8847,13 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43372</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43462</v>
       </c>
-      <c r="C39" s="1" t="n">
+      <c r="C39" s="2" t="n">
         <v>43500</v>
       </c>
       <c r="D39" t="inlineStr">
@@ -8868,7 +8880,7 @@
       <c r="I39" t="n">
         <v>5.760000000000001</v>
       </c>
-      <c r="J39" s="1" t="n">
+      <c r="J39" s="2" t="n">
         <v>43500</v>
       </c>
       <c r="K39" t="n">
@@ -8881,13 +8893,13 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43463</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43553</v>
       </c>
-      <c r="C40" s="1" t="n">
+      <c r="C40" s="2" t="n">
         <v>43585</v>
       </c>
       <c r="D40" t="inlineStr">
@@ -8914,7 +8926,7 @@
       <c r="I40" t="n">
         <v>5.140000000000001</v>
       </c>
-      <c r="J40" s="1" t="n">
+      <c r="J40" s="2" t="n">
         <v>43585</v>
       </c>
       <c r="K40" t="n">
@@ -8927,13 +8939,13 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43554</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43644</v>
       </c>
-      <c r="C41" s="1" t="n">
+      <c r="C41" s="2" t="n">
         <v>43679</v>
       </c>
       <c r="D41" t="inlineStr">
@@ -8960,7 +8972,7 @@
       <c r="I41" t="n">
         <v>7.06</v>
       </c>
-      <c r="J41" s="1" t="n">
+      <c r="J41" s="2" t="n">
         <v>43679</v>
       </c>
       <c r="K41" t="n">
@@ -8973,13 +8985,13 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43645</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43742</v>
       </c>
-      <c r="C42" s="1" t="n">
+      <c r="C42" s="2" t="n">
         <v>43770</v>
       </c>
       <c r="D42" t="inlineStr">
@@ -9006,7 +9018,7 @@
       <c r="I42" t="n">
         <v>6.260000000000001</v>
       </c>
-      <c r="J42" s="1" t="n">
+      <c r="J42" s="2" t="n">
         <v>43770</v>
       </c>
       <c r="K42" t="n">
@@ -9019,13 +9031,13 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43743</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43833</v>
       </c>
-      <c r="C43" s="1" t="n">
+      <c r="C43" s="2" t="n">
         <v>43866</v>
       </c>
       <c r="D43" t="inlineStr">
@@ -9052,7 +9064,7 @@
       <c r="I43" t="n">
         <v>6.119999999999999</v>
       </c>
-      <c r="J43" s="1" t="n">
+      <c r="J43" s="2" t="n">
         <v>43866</v>
       </c>
       <c r="K43" t="n">
@@ -9065,13 +9077,13 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43834</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43924</v>
       </c>
-      <c r="C44" s="1" t="n">
+      <c r="C44" s="2" t="n">
         <v>43951</v>
       </c>
       <c r="D44" t="inlineStr">
@@ -9098,7 +9110,7 @@
       <c r="I44" t="n">
         <v>6.65</v>
       </c>
-      <c r="J44" s="1" t="n">
+      <c r="J44" s="2" t="n">
         <v>43951</v>
       </c>
       <c r="K44" t="n">
@@ -9111,13 +9123,13 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>43925</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>44015</v>
       </c>
-      <c r="C45" s="1" t="n">
+      <c r="C45" s="2" t="n">
         <v>44050</v>
       </c>
       <c r="D45" t="inlineStr">
@@ -9144,7 +9156,7 @@
       <c r="I45" t="n">
         <v>3.79</v>
       </c>
-      <c r="J45" s="1" t="n">
+      <c r="J45" s="2" t="n">
         <v>44050</v>
       </c>
       <c r="K45" t="n">
@@ -9157,13 +9169,13 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>44016</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>44106</v>
       </c>
-      <c r="C46" s="1" t="n">
+      <c r="C46" s="2" t="n">
         <v>44133</v>
       </c>
       <c r="D46" t="inlineStr">
@@ -9190,7 +9202,7 @@
       <c r="I46" t="n">
         <v>3.91</v>
       </c>
-      <c r="J46" s="1" t="n">
+      <c r="J46" s="2" t="n">
         <v>44133</v>
       </c>
       <c r="K46" t="n">
@@ -9203,13 +9215,13 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>44107</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>44197</v>
       </c>
-      <c r="C47" s="1" t="n">
+      <c r="C47" s="2" t="n">
         <v>44224</v>
       </c>
       <c r="D47" t="inlineStr">
@@ -9236,7 +9248,7 @@
       <c r="I47" t="n">
         <v>3.830000000000001</v>
       </c>
-      <c r="J47" s="1" t="n">
+      <c r="J47" s="2" t="n">
         <v>44224</v>
       </c>
       <c r="K47" t="n">
@@ -9249,13 +9261,13 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>44198</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>44288</v>
       </c>
-      <c r="C48" s="1" t="n">
+      <c r="C48" s="2" t="n">
         <v>44315</v>
       </c>
       <c r="D48" t="inlineStr">
@@ -9282,7 +9294,7 @@
       <c r="I48" t="n">
         <v>4</v>
       </c>
-      <c r="J48" s="1" t="n">
+      <c r="J48" s="2" t="n">
         <v>44315</v>
       </c>
       <c r="K48" t="n">
@@ -9295,13 +9307,13 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>44289</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44379</v>
       </c>
-      <c r="C49" s="1" t="n">
+      <c r="C49" s="2" t="n">
         <v>44414</v>
       </c>
       <c r="D49" t="inlineStr">
@@ -9328,7 +9340,7 @@
       <c r="I49" t="n">
         <v>5.36</v>
       </c>
-      <c r="J49" s="1" t="n">
+      <c r="J49" s="2" t="n">
         <v>44414</v>
       </c>
       <c r="K49" t="n">
@@ -9341,13 +9353,13 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44380</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44470</v>
       </c>
-      <c r="C50" s="1" t="n">
+      <c r="C50" s="2" t="n">
         <v>44497</v>
       </c>
       <c r="D50" t="inlineStr">
@@ -9374,7 +9386,7 @@
       <c r="I50" t="n">
         <v>6.780000000000001</v>
       </c>
-      <c r="J50" s="1" t="n">
+      <c r="J50" s="2" t="n">
         <v>44497</v>
       </c>
       <c r="K50" t="n">
@@ -9387,13 +9399,13 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44471</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44561</v>
       </c>
-      <c r="C51" s="1" t="n">
+      <c r="C51" s="2" t="n">
         <v>44588</v>
       </c>
       <c r="D51" t="inlineStr">
@@ -9420,7 +9432,7 @@
       <c r="I51" t="n">
         <v>7.890000000000001</v>
       </c>
-      <c r="J51" s="1" t="n">
+      <c r="J51" s="2" t="n">
         <v>44588</v>
       </c>
       <c r="K51" t="n">
@@ -9433,13 +9445,13 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44562</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44652</v>
       </c>
-      <c r="C52" s="1" t="n">
+      <c r="C52" s="2" t="n">
         <v>44679</v>
       </c>
       <c r="D52" t="inlineStr">
@@ -9466,7 +9478,7 @@
       <c r="I52" t="n">
         <v>8.06</v>
       </c>
-      <c r="J52" s="1" t="n">
+      <c r="J52" s="2" t="n">
         <v>44679</v>
       </c>
       <c r="K52" t="n">
@@ -9479,13 +9491,13 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44653</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44743</v>
       </c>
-      <c r="C53" s="1" t="n">
+      <c r="C53" s="2" t="n">
         <v>44778</v>
       </c>
       <c r="D53" t="inlineStr">
@@ -9512,7 +9524,7 @@
       <c r="I53" t="n">
         <v>7.36</v>
       </c>
-      <c r="J53" s="1" t="n">
+      <c r="J53" s="2" t="n">
         <v>44778</v>
       </c>
       <c r="K53" t="n">
@@ -9525,13 +9537,13 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44744</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44834</v>
       </c>
-      <c r="C54" s="1" t="n">
+      <c r="C54" s="2" t="n">
         <v>44861</v>
       </c>
       <c r="D54" t="inlineStr">
@@ -9558,7 +9570,7 @@
       <c r="I54" t="n">
         <v>5.220000000000001</v>
       </c>
-      <c r="J54" s="1" t="n">
+      <c r="J54" s="2" t="n">
         <v>44861</v>
       </c>
       <c r="K54" t="n">
@@ -9571,13 +9583,13 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44835</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44925</v>
       </c>
-      <c r="C55" s="1" t="n">
+      <c r="C55" s="2" t="n">
         <v>44951</v>
       </c>
       <c r="D55" t="inlineStr">
@@ -9604,7 +9616,7 @@
       <c r="I55" t="n">
         <v>2.830000000000001</v>
       </c>
-      <c r="J55" s="1" t="n">
+      <c r="J55" s="2" t="n">
         <v>44951</v>
       </c>
       <c r="K55" t="n">
@@ -9617,13 +9629,13 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44926</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>45016</v>
       </c>
-      <c r="C56" s="1" t="n">
+      <c r="C56" s="2" t="n">
         <v>45042</v>
       </c>
       <c r="D56" t="inlineStr">
@@ -9650,7 +9662,7 @@
       <c r="I56" t="n">
         <v>-0.819999999999999</v>
       </c>
-      <c r="J56" s="1" t="n">
+      <c r="J56" s="2" t="n">
         <v>45042</v>
       </c>
       <c r="K56" t="n">
@@ -9663,13 +9675,13 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>45017</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>45107</v>
       </c>
-      <c r="C57" s="1" t="n">
+      <c r="C57" s="2" t="n">
         <v>45142</v>
       </c>
       <c r="D57" t="inlineStr">
@@ -9696,7 +9708,7 @@
       <c r="I57" t="n">
         <v>-2.559999999999999</v>
       </c>
-      <c r="J57" s="1" t="n">
+      <c r="J57" s="2" t="n">
         <v>45142</v>
       </c>
       <c r="K57" t="n">
@@ -9709,13 +9721,13 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>45108</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>45198</v>
       </c>
-      <c r="C58" s="1" t="n">
+      <c r="C58" s="2" t="n">
         <v>45226</v>
       </c>
       <c r="D58" t="inlineStr">
@@ -9742,7 +9754,7 @@
       <c r="I58" t="n">
         <v>-3.579999999999999</v>
       </c>
-      <c r="J58" s="1" t="n">
+      <c r="J58" s="2" t="n">
         <v>45226</v>
       </c>
       <c r="K58" t="n">
@@ -9755,13 +9767,13 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>45199</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>45289</v>
       </c>
-      <c r="C59" s="1" t="n">
+      <c r="C59" s="2" t="n">
         <v>45317</v>
       </c>
       <c r="D59" t="inlineStr">
@@ -9788,7 +9800,7 @@
       <c r="I59" t="n">
         <v>-3.509999999999999</v>
       </c>
-      <c r="J59" s="1" t="n">
+      <c r="J59" s="2" t="n">
         <v>45317</v>
       </c>
       <c r="K59" t="n">
@@ -9801,13 +9813,13 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>45290</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45380</v>
       </c>
-      <c r="C60" s="1" t="n">
+      <c r="C60" s="2" t="n">
         <v>45408</v>
       </c>
       <c r="D60" t="inlineStr">
@@ -9834,7 +9846,7 @@
       <c r="I60" t="n">
         <v>-1.299999999999999</v>
       </c>
-      <c r="J60" s="1" t="n">
+      <c r="J60" s="2" t="n">
         <v>45408</v>
       </c>
       <c r="K60" t="n">
@@ -9847,13 +9859,13 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45381</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45471</v>
       </c>
-      <c r="C61" s="1" t="n">
+      <c r="C61" s="2" t="n">
         <v>45506</v>
       </c>
       <c r="D61" t="inlineStr">
@@ -9880,7 +9892,7 @@
       <c r="I61" t="n">
         <v>1.580000000000001</v>
       </c>
-      <c r="J61" s="1" t="n">
+      <c r="J61" s="2" t="n">
         <v>45506</v>
       </c>
       <c r="K61" t="n">
@@ -9893,13 +9905,13 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45472</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45562</v>
       </c>
-      <c r="C62" s="1" t="n">
+      <c r="C62" s="2" t="n">
         <v>45590</v>
       </c>
       <c r="D62" t="inlineStr">
@@ -9926,7 +9938,7 @@
       <c r="I62" t="n">
         <v>3.870000000000001</v>
       </c>
-      <c r="J62" s="1" t="n">
+      <c r="J62" s="2" t="n">
         <v>45590</v>
       </c>
       <c r="K62" t="n">
@@ -9939,13 +9951,13 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45563</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45653</v>
       </c>
-      <c r="C63" s="1" t="n">
+      <c r="C63" s="2" t="n">
         <v>45681</v>
       </c>
       <c r="D63" t="inlineStr">
@@ -9972,7 +9984,7 @@
       <c r="I63" t="n">
         <v>5.510000000000002</v>
       </c>
-      <c r="J63" s="1" t="n">
+      <c r="J63" s="2" t="n">
         <v>45681</v>
       </c>
       <c r="K63" t="n">
@@ -9985,13 +9997,13 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45654</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45744</v>
       </c>
-      <c r="C64" s="1" t="n">
+      <c r="C64" s="2" t="n">
         <v>45779</v>
       </c>
       <c r="D64" t="inlineStr">
@@ -10018,7 +10030,7 @@
       <c r="I64" t="n">
         <v>6.960000000000001</v>
       </c>
-      <c r="J64" s="1" t="n">
+      <c r="J64" s="2" t="n">
         <v>45779</v>
       </c>
       <c r="K64" t="n">
@@ -10031,13 +10043,13 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45745</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45835</v>
       </c>
-      <c r="C65" s="1" t="n">
+      <c r="C65" s="2" t="n">
         <v>45870</v>
       </c>
       <c r="D65" t="inlineStr">
@@ -10064,7 +10076,7 @@
       <c r="I65" t="n">
         <v>6.77</v>
       </c>
-      <c r="J65" s="1" t="n">
+      <c r="J65" s="2" t="n">
         <v>45870</v>
       </c>
       <c r="K65" t="n">
@@ -10077,13 +10089,13 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45836</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45933</v>
       </c>
-      <c r="C66" s="1" t="n">
+      <c r="C66" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="D66" t="inlineStr">
@@ -10110,7 +10122,7 @@
       <c r="I66" t="n">
         <v>7.790000000000001</v>
       </c>
-      <c r="J66" s="1" t="n">
+      <c r="J66" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="K66" t="n">
@@ -10123,13 +10135,13 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45934</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>46024</v>
       </c>
-      <c r="C67" s="1" t="n">
+      <c r="C67" s="2" t="n">
         <v>46052</v>
       </c>
       <c r="D67" t="inlineStr">
@@ -10156,7 +10168,7 @@
       <c r="I67" t="n">
         <v>8.84</v>
       </c>
-      <c r="J67" s="1" t="n">
+      <c r="J67" s="2" t="n">
         <v>46052</v>
       </c>
       <c r="K67" t="n">
@@ -10169,13 +10181,13 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>46025</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>46115</v>
       </c>
-      <c r="C68" s="1" t="n">
+      <c r="C68" s="2" t="n">
         <v>46141</v>
       </c>
       <c r="D68" t="inlineStr">
@@ -10202,7 +10214,7 @@
       <c r="I68" t="n">
         <v>10.54</v>
       </c>
-      <c r="J68" s="1" t="n">
+      <c r="J68" s="2" t="n">
         <v>46141</v>
       </c>
       <c r="K68" t="n">
@@ -10215,13 +10227,13 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>46116</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>46206</v>
       </c>
-      <c r="C69" s="1" t="n">
+      <c r="C69" s="2" t="n">
         <v>46238</v>
       </c>
       <c r="D69" t="inlineStr">
@@ -10248,7 +10260,7 @@
       <c r="I69" t="n">
         <v>13.9</v>
       </c>
-      <c r="J69" s="1" t="n">
+      <c r="J69" s="2" t="n">
         <v>46238</v>
       </c>
       <c r="K69" t="n">
@@ -10285,52 +10297,52 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>acciones</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>40478</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>40485</v>
       </c>
       <c r="C2" t="n">
@@ -10359,10 +10371,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>40569</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>40577</v>
       </c>
       <c r="C3" t="n">
@@ -10391,10 +10403,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>40659</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>40666</v>
       </c>
       <c r="C4" t="n">
@@ -10423,10 +10435,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>40766</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>40772</v>
       </c>
       <c r="C5" t="n">
@@ -10455,10 +10467,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>40840</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40843</v>
       </c>
       <c r="C6" t="n">
@@ -10487,10 +10499,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40933</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40940</v>
       </c>
       <c r="C7" t="n">
@@ -10519,10 +10531,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>41024</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>41029</v>
       </c>
       <c r="C8" t="n">
@@ -10551,10 +10563,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>41120</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>41130</v>
       </c>
       <c r="C9" t="n">
@@ -10583,10 +10595,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>41302</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>41303</v>
       </c>
       <c r="C10" t="n">
@@ -10615,10 +10627,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>41390</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>41396</v>
       </c>
       <c r="C11" t="n">
@@ -10647,10 +10659,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>41486</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>41494</v>
       </c>
       <c r="C12" t="n">
@@ -10679,10 +10691,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>41572</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>41576</v>
       </c>
       <c r="C13" t="n">
@@ -10711,10 +10723,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>41663</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>41667</v>
       </c>
       <c r="C14" t="n">
@@ -10743,10 +10755,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>41754</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>41759</v>
       </c>
       <c r="C15" t="n">
@@ -10775,10 +10787,10 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>41845</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>41859</v>
       </c>
       <c r="C16" t="n">
@@ -10807,10 +10819,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41939</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41946</v>
       </c>
       <c r="C17" t="n">
@@ -10839,10 +10851,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>42030</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>42034</v>
       </c>
       <c r="C18" t="n">
@@ -10871,10 +10883,10 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>42220</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>42228</v>
       </c>
       <c r="C19" t="n">
@@ -10903,10 +10915,10 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>42303</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>42307</v>
       </c>
       <c r="C20" t="n">
@@ -10935,10 +10947,10 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>42394</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>42398</v>
       </c>
       <c r="C21" t="n">
@@ -10967,10 +10979,10 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>42485</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>42489</v>
       </c>
       <c r="C22" t="n">
@@ -10999,10 +11011,10 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>42580</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>42587</v>
       </c>
       <c r="C23" t="n">
@@ -11031,10 +11043,10 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>42667</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>42671</v>
       </c>
       <c r="C24" t="n">
@@ -11063,10 +11075,10 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>42758</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>42761</v>
       </c>
       <c r="C25" t="n">
@@ -11095,10 +11107,10 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>42849</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>42853</v>
       </c>
       <c r="C26" t="n">
@@ -11127,10 +11139,10 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>42947</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42951</v>
       </c>
       <c r="C27" t="n">
@@ -11159,10 +11171,10 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>43031</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>43035</v>
       </c>
       <c r="C28" t="n">
@@ -11191,10 +11203,10 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>43123</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>43129</v>
       </c>
       <c r="C29" t="n">
@@ -11223,10 +11235,10 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>43215</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>43221</v>
       </c>
       <c r="C30" t="n">
@@ -11255,10 +11267,10 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>43311</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>43315</v>
       </c>
       <c r="C31" t="n">
@@ -11287,10 +11299,10 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>43402</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>43406</v>
       </c>
       <c r="C32" t="n">
@@ -11319,10 +11331,10 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>43494</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>43500</v>
       </c>
       <c r="C33" t="n">
@@ -11351,10 +11363,10 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>43579</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>43585</v>
       </c>
       <c r="C34" t="n">
@@ -11383,10 +11395,10 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>43675</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>43679</v>
       </c>
       <c r="C35" t="n">
@@ -11415,10 +11427,10 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>43766</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>43770</v>
       </c>
       <c r="C36" t="n">
@@ -11447,10 +11459,10 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>43861</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>43866</v>
       </c>
       <c r="C37" t="n">
@@ -11479,10 +11491,10 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>43948</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43951</v>
       </c>
       <c r="C38" t="n">
@@ -11511,10 +11523,10 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>44046</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>44050</v>
       </c>
       <c r="C39" t="n">
@@ -11543,10 +11555,10 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>44130</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>44133</v>
       </c>
       <c r="C40" t="n">
@@ -11575,10 +11587,10 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>44221</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>44224</v>
       </c>
       <c r="C41" t="n">
@@ -11607,10 +11619,10 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>44312</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>44315</v>
       </c>
       <c r="C42" t="n">
@@ -11639,10 +11651,10 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>44410</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>44414</v>
       </c>
       <c r="C43" t="n">
@@ -11671,10 +11683,10 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>44494</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>44497</v>
       </c>
       <c r="C44" t="n">
@@ -11703,10 +11715,10 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>44585</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>44588</v>
       </c>
       <c r="C45" t="n">
@@ -11735,10 +11747,10 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>44676</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>44679</v>
       </c>
       <c r="C46" t="n">
@@ -11767,10 +11779,10 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>44774</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>44778</v>
       </c>
       <c r="C47" t="n">
@@ -11799,10 +11811,10 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>44858</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>44861</v>
       </c>
       <c r="C48" t="n">
@@ -11831,10 +11843,10 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>44949</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44951</v>
       </c>
       <c r="C49" t="n">
@@ -11863,10 +11875,10 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>45040</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>45042</v>
       </c>
       <c r="C50" t="n">
@@ -11895,10 +11907,10 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>45138</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>45142</v>
       </c>
       <c r="C51" t="n">
@@ -11927,10 +11939,10 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>45222</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>45226</v>
       </c>
       <c r="C52" t="n">
@@ -11959,10 +11971,10 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>45313</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>45317</v>
       </c>
       <c r="C53" t="n">
@@ -11991,10 +12003,10 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>45404</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>45408</v>
       </c>
       <c r="C54" t="n">
@@ -12023,10 +12035,10 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>45503</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>45506</v>
       </c>
       <c r="C55" t="n">
@@ -12055,10 +12067,10 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>45588</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>45590</v>
       </c>
       <c r="C56" t="n">
@@ -12087,10 +12099,10 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>45679</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>45681</v>
       </c>
       <c r="C57" t="n">
@@ -12119,10 +12131,10 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>45776</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>45779</v>
       </c>
       <c r="C58" t="n">
@@ -12151,10 +12163,10 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>45867</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>45870</v>
       </c>
       <c r="C59" t="n">
@@ -12183,10 +12195,10 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>45958</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="C60" t="n">
@@ -12215,10 +12227,10 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>46049</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>46052</v>
       </c>
       <c r="C61" t="n">
@@ -12247,10 +12259,10 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>46139</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>46141</v>
       </c>
       <c r="C62" t="n">
@@ -12279,10 +12291,10 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>46234</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>46238</v>
       </c>
       <c r="C63" t="n">
@@ -12329,12 +12341,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>campo</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>valor</t>
         </is>

--- a/salidas/empresas/STX.xlsx
+++ b/salidas/empresas/STX.xlsx
@@ -498,7 +498,7 @@
         <v>38748</v>
       </c>
       <c r="B2" t="n">
-        <v>12.50734233856201</v>
+        <v>12.50733852386475</v>
       </c>
       <c r="C2" t="n">
         <v>26.07999992370605</v>
@@ -517,7 +517,7 @@
         <v>38776</v>
       </c>
       <c r="B3" t="n">
-        <v>12.78153991699219</v>
+        <v>12.78153800964355</v>
       </c>
       <c r="C3" t="n">
         <v>26.56999969482422</v>
@@ -536,7 +536,7 @@
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>12.66609287261963</v>
+        <v>12.6660852432251</v>
       </c>
       <c r="C4" t="n">
         <v>26.32999992370605</v>
@@ -555,7 +555,7 @@
         <v>38837</v>
       </c>
       <c r="B5" t="n">
-        <v>12.7767276763916</v>
+        <v>12.77672863006592</v>
       </c>
       <c r="C5" t="n">
         <v>26.55999946594238</v>
@@ -593,7 +593,7 @@
         <v>38898</v>
       </c>
       <c r="B7" t="n">
-        <v>10.92367458343506</v>
+        <v>10.92367744445801</v>
       </c>
       <c r="C7" t="n">
         <v>22.63999938964844</v>
@@ -612,7 +612,7 @@
         <v>38929</v>
       </c>
       <c r="B8" t="n">
-        <v>11.19387245178223</v>
+        <v>11.19387626647949</v>
       </c>
       <c r="C8" t="n">
         <v>23.20000076293945</v>
@@ -631,7 +631,7 @@
         <v>38960</v>
       </c>
       <c r="B9" t="n">
-        <v>10.77705192565918</v>
+        <v>10.77704906463623</v>
       </c>
       <c r="C9" t="n">
         <v>22.25</v>
@@ -650,7 +650,7 @@
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>11.18391704559326</v>
+        <v>11.18392086029053</v>
       </c>
       <c r="C10" t="n">
         <v>23.09000015258789</v>
@@ -669,7 +669,7 @@
         <v>39021</v>
       </c>
       <c r="B11" t="n">
-        <v>10.93689060211182</v>
+        <v>10.9368896484375</v>
       </c>
       <c r="C11" t="n">
         <v>22.57999992370605</v>
@@ -688,7 +688,7 @@
         <v>39051</v>
       </c>
       <c r="B12" t="n">
-        <v>12.53266525268555</v>
+        <v>12.53266906738281</v>
       </c>
       <c r="C12" t="n">
         <v>25.76000022888184</v>
@@ -707,7 +707,7 @@
         <v>39082</v>
       </c>
       <c r="B13" t="n">
-        <v>12.89268684387207</v>
+        <v>12.89268779754639</v>
       </c>
       <c r="C13" t="n">
         <v>26.5</v>
@@ -726,7 +726,7 @@
         <v>39113</v>
       </c>
       <c r="B14" t="n">
-        <v>13.22763919830322</v>
+        <v>13.22764110565186</v>
       </c>
       <c r="C14" t="n">
         <v>27.09000015258789</v>
@@ -745,7 +745,7 @@
         <v>39141</v>
       </c>
       <c r="B15" t="n">
-        <v>13.13486480712891</v>
+        <v>13.13486576080322</v>
       </c>
       <c r="C15" t="n">
         <v>26.89999961853027</v>
@@ -764,7 +764,7 @@
         <v>39172</v>
       </c>
       <c r="B16" t="n">
-        <v>11.37703800201416</v>
+        <v>11.37704086303711</v>
       </c>
       <c r="C16" t="n">
         <v>23.29999923706055</v>
@@ -783,7 +783,7 @@
         <v>39202</v>
       </c>
       <c r="B17" t="n">
-        <v>10.81551456451416</v>
+        <v>10.81551551818848</v>
       </c>
       <c r="C17" t="n">
         <v>22.14999961853027</v>
@@ -802,7 +802,7 @@
         <v>39233</v>
       </c>
       <c r="B18" t="n">
-        <v>10.10055541992188</v>
+        <v>10.10055065155029</v>
       </c>
       <c r="C18" t="n">
         <v>20.59000015258789</v>
@@ -840,7 +840,7 @@
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>11.53297233581543</v>
+        <v>11.53296756744385</v>
       </c>
       <c r="C20" t="n">
         <v>23.51000022888184</v>
@@ -859,7 +859,7 @@
         <v>39325</v>
       </c>
       <c r="B21" t="n">
-        <v>12.72026538848877</v>
+        <v>12.72026348114014</v>
       </c>
       <c r="C21" t="n">
         <v>25.81999969482422</v>
@@ -878,7 +878,7 @@
         <v>39355</v>
       </c>
       <c r="B22" t="n">
-        <v>12.60203456878662</v>
+        <v>12.60202980041504</v>
       </c>
       <c r="C22" t="n">
         <v>25.57999992370605</v>
@@ -897,7 +897,7 @@
         <v>39386</v>
       </c>
       <c r="B23" t="n">
-        <v>13.76644611358643</v>
+        <v>13.76644802093506</v>
       </c>
       <c r="C23" t="n">
         <v>27.84000015258789</v>
@@ -916,7 +916,7 @@
         <v>39416</v>
       </c>
       <c r="B24" t="n">
-        <v>12.75275325775146</v>
+        <v>12.75275135040283</v>
       </c>
       <c r="C24" t="n">
         <v>25.79000091552734</v>
@@ -954,7 +954,7 @@
         <v>39478</v>
       </c>
       <c r="B26" t="n">
-        <v>10.07255077362061</v>
+        <v>10.07254600524902</v>
       </c>
       <c r="C26" t="n">
         <v>20.27000045776367</v>
@@ -973,7 +973,7 @@
         <v>39507</v>
       </c>
       <c r="B27" t="n">
-        <v>10.71854782104492</v>
+        <v>10.71854591369629</v>
       </c>
       <c r="C27" t="n">
         <v>21.56999969482422</v>
@@ -992,7 +992,7 @@
         <v>39538</v>
       </c>
       <c r="B28" t="n">
-        <v>10.40548610687256</v>
+        <v>10.40548229217529</v>
       </c>
       <c r="C28" t="n">
         <v>20.94000053405762</v>
@@ -1011,7 +1011,7 @@
         <v>39568</v>
       </c>
       <c r="B29" t="n">
-        <v>9.435839653015137</v>
+        <v>9.435837745666504</v>
       </c>
       <c r="C29" t="n">
         <v>18.8700008392334</v>
@@ -1030,7 +1030,7 @@
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>10.71095085144043</v>
+        <v>10.71095275878906</v>
       </c>
       <c r="C30" t="n">
         <v>21.42000007629395</v>
@@ -1068,7 +1068,7 @@
         <v>39660</v>
       </c>
       <c r="B32" t="n">
-        <v>7.545631885528564</v>
+        <v>7.545629024505615</v>
       </c>
       <c r="C32" t="n">
         <v>14.97000026702881</v>
@@ -1087,7 +1087,7 @@
         <v>39691</v>
       </c>
       <c r="B33" t="n">
-        <v>7.515387535095215</v>
+        <v>7.515387058258057</v>
       </c>
       <c r="C33" t="n">
         <v>14.90999984741211</v>
@@ -1106,7 +1106,7 @@
         <v>39721</v>
       </c>
       <c r="B34" t="n">
-        <v>6.10908842086792</v>
+        <v>6.109087467193604</v>
       </c>
       <c r="C34" t="n">
         <v>12.11999988555908</v>
@@ -1163,7 +1163,7 @@
         <v>39813</v>
       </c>
       <c r="B37" t="n">
-        <v>2.269102811813354</v>
+        <v>2.269103050231934</v>
       </c>
       <c r="C37" t="n">
         <v>4.429999828338623</v>
@@ -1182,7 +1182,7 @@
         <v>39844</v>
       </c>
       <c r="B38" t="n">
-        <v>1.941287875175476</v>
+        <v>1.941285967826843</v>
       </c>
       <c r="C38" t="n">
         <v>3.789999961853027</v>
@@ -1201,7 +1201,7 @@
         <v>39872</v>
       </c>
       <c r="B39" t="n">
-        <v>2.219903230667114</v>
+        <v>2.219903469085693</v>
       </c>
       <c r="C39" t="n">
         <v>4.300000190734863</v>
@@ -1220,7 +1220,7 @@
         <v>39903</v>
       </c>
       <c r="B40" t="n">
-        <v>3.102701902389526</v>
+        <v>3.102702856063843</v>
       </c>
       <c r="C40" t="n">
         <v>6.010000228881836</v>
@@ -1296,7 +1296,7 @@
         <v>40025</v>
       </c>
       <c r="B44" t="n">
-        <v>6.215729713439941</v>
+        <v>6.215728759765625</v>
       </c>
       <c r="C44" t="n">
         <v>12.03999996185303</v>
@@ -1315,7 +1315,7 @@
         <v>40056</v>
       </c>
       <c r="B45" t="n">
-        <v>7.150156497955322</v>
+        <v>7.15015697479248</v>
       </c>
       <c r="C45" t="n">
         <v>13.85000038146973</v>
@@ -1353,7 +1353,7 @@
         <v>40117</v>
       </c>
       <c r="B47" t="n">
-        <v>7.201779365539551</v>
+        <v>7.201778888702393</v>
       </c>
       <c r="C47" t="n">
         <v>13.94999980926514</v>
@@ -1372,7 +1372,7 @@
         <v>40147</v>
       </c>
       <c r="B48" t="n">
-        <v>7.810963153839111</v>
+        <v>7.810962200164795</v>
       </c>
       <c r="C48" t="n">
         <v>15.13000011444092</v>
@@ -1391,7 +1391,7 @@
         <v>40178</v>
       </c>
       <c r="B49" t="n">
-        <v>9.390707969665527</v>
+        <v>9.390707015991211</v>
       </c>
       <c r="C49" t="n">
         <v>18.19000053405762</v>
@@ -1410,7 +1410,7 @@
         <v>40209</v>
       </c>
       <c r="B50" t="n">
-        <v>8.626646995544434</v>
+        <v>8.626646041870117</v>
       </c>
       <c r="C50" t="n">
         <v>16.70999908447266</v>
@@ -1429,7 +1429,7 @@
         <v>40237</v>
       </c>
       <c r="B51" t="n">
-        <v>10.27866649627686</v>
+        <v>10.27867031097412</v>
       </c>
       <c r="C51" t="n">
         <v>19.90999984741211</v>
@@ -1448,7 +1448,7 @@
         <v>40268</v>
       </c>
       <c r="B52" t="n">
-        <v>9.426840782165527</v>
+        <v>9.426844596862793</v>
       </c>
       <c r="C52" t="n">
         <v>18.26000022888184</v>
@@ -1467,7 +1467,7 @@
         <v>40298</v>
       </c>
       <c r="B53" t="n">
-        <v>9.473306655883789</v>
+        <v>9.473312377929688</v>
       </c>
       <c r="C53" t="n">
         <v>18.35000038146973</v>
@@ -1486,7 +1486,7 @@
         <v>40329</v>
       </c>
       <c r="B54" t="n">
-        <v>7.929703235626221</v>
+        <v>7.929699897766113</v>
       </c>
       <c r="C54" t="n">
         <v>15.35999965667725</v>
@@ -1505,7 +1505,7 @@
         <v>40359</v>
       </c>
       <c r="B55" t="n">
-        <v>6.731986999511719</v>
+        <v>6.731985569000244</v>
       </c>
       <c r="C55" t="n">
         <v>13.03999996185303</v>
@@ -1524,7 +1524,7 @@
         <v>40390</v>
       </c>
       <c r="B56" t="n">
-        <v>6.479022026062012</v>
+        <v>6.479020595550537</v>
       </c>
       <c r="C56" t="n">
         <v>12.55000019073486</v>
@@ -1543,7 +1543,7 @@
         <v>40421</v>
       </c>
       <c r="B57" t="n">
-        <v>5.234842300415039</v>
+        <v>5.234841823577881</v>
       </c>
       <c r="C57" t="n">
         <v>10.14000034332275</v>
@@ -1581,7 +1581,7 @@
         <v>40482</v>
       </c>
       <c r="B59" t="n">
-        <v>7.594136238098145</v>
+        <v>7.594132423400879</v>
       </c>
       <c r="C59" t="n">
         <v>14.71000003814697</v>
@@ -1600,7 +1600,7 @@
         <v>40512</v>
       </c>
       <c r="B60" t="n">
-        <v>6.923002243041992</v>
+        <v>6.922999858856201</v>
       </c>
       <c r="C60" t="n">
         <v>13.40999984741211</v>
@@ -1625,7 +1625,7 @@
         <v>40543</v>
       </c>
       <c r="B61" t="n">
-        <v>7.759337902069092</v>
+        <v>7.759336471557617</v>
       </c>
       <c r="C61" t="n">
         <v>15.02999973297119</v>
@@ -1650,7 +1650,7 @@
         <v>40574</v>
       </c>
       <c r="B62" t="n">
-        <v>7.22758960723877</v>
+        <v>7.227592468261719</v>
       </c>
       <c r="C62" t="n">
         <v>14</v>
@@ -1675,7 +1675,7 @@
         <v>40602</v>
       </c>
       <c r="B63" t="n">
-        <v>6.556461334228516</v>
+        <v>6.556458473205566</v>
       </c>
       <c r="C63" t="n">
         <v>12.69999980926514</v>
@@ -1700,7 +1700,7 @@
         <v>40633</v>
       </c>
       <c r="B64" t="n">
-        <v>7.439258575439453</v>
+        <v>7.439259052276611</v>
       </c>
       <c r="C64" t="n">
         <v>14.40999984741211</v>
@@ -1725,7 +1725,7 @@
         <v>40663</v>
       </c>
       <c r="B65" t="n">
-        <v>9.188530921936035</v>
+        <v>9.188535690307617</v>
       </c>
       <c r="C65" t="n">
         <v>17.6200008392334</v>
@@ -1750,7 +1750,7 @@
         <v>40694</v>
       </c>
       <c r="B66" t="n">
-        <v>8.760915756225586</v>
+        <v>8.760912895202637</v>
       </c>
       <c r="C66" t="n">
         <v>16.79999923706055</v>
@@ -1800,7 +1800,7 @@
         <v>40755</v>
       </c>
       <c r="B68" t="n">
-        <v>7.243398189544678</v>
+        <v>7.24340295791626</v>
       </c>
       <c r="C68" t="n">
         <v>13.89000034332275</v>
@@ -1825,7 +1825,7 @@
         <v>40786</v>
       </c>
       <c r="B69" t="n">
-        <v>6.12225866317749</v>
+        <v>6.122257709503174</v>
       </c>
       <c r="C69" t="n">
         <v>11.57999992370605</v>
@@ -1854,7 +1854,7 @@
         <v>40816</v>
       </c>
       <c r="B70" t="n">
-        <v>5.434958457946777</v>
+        <v>5.434960842132568</v>
       </c>
       <c r="C70" t="n">
         <v>10.27999973297119</v>
@@ -1883,7 +1883,7 @@
         <v>40847</v>
       </c>
       <c r="B71" t="n">
-        <v>8.538382530212402</v>
+        <v>8.538383483886719</v>
       </c>
       <c r="C71" t="n">
         <v>16.14999961853027</v>
@@ -1912,7 +1912,7 @@
         <v>40877</v>
       </c>
       <c r="B72" t="n">
-        <v>9.142539978027344</v>
+        <v>9.142538070678711</v>
       </c>
       <c r="C72" t="n">
         <v>17.10000038146973</v>
@@ -1941,7 +1941,7 @@
         <v>40908</v>
       </c>
       <c r="B73" t="n">
-        <v>8.768282890319824</v>
+        <v>8.76828670501709</v>
       </c>
       <c r="C73" t="n">
         <v>16.39999961853027</v>
@@ -1970,7 +1970,7 @@
         <v>40939</v>
       </c>
       <c r="B74" t="n">
-        <v>11.30253124237061</v>
+        <v>11.30253219604492</v>
       </c>
       <c r="C74" t="n">
         <v>21.13999938964844</v>
@@ -1999,7 +1999,7 @@
         <v>40968</v>
       </c>
       <c r="B75" t="n">
-        <v>14.17520999908447</v>
+        <v>14.17520809173584</v>
       </c>
       <c r="C75" t="n">
         <v>26.26000022888184</v>
@@ -2028,7 +2028,7 @@
         <v>40999</v>
       </c>
       <c r="B76" t="n">
-        <v>14.55307006835938</v>
+        <v>14.55307483673096</v>
       </c>
       <c r="C76" t="n">
         <v>26.95999908447266</v>
@@ -2057,7 +2057,7 @@
         <v>41029</v>
       </c>
       <c r="B77" t="n">
-        <v>16.74585151672363</v>
+        <v>16.745849609375</v>
       </c>
       <c r="C77" t="n">
         <v>30.76000022888184</v>
@@ -2086,7 +2086,7 @@
         <v>41060</v>
       </c>
       <c r="B78" t="n">
-        <v>12.75537014007568</v>
+        <v>12.75537395477295</v>
       </c>
       <c r="C78" t="n">
         <v>23.43000030517578</v>
@@ -2115,7 +2115,7 @@
         <v>41090</v>
       </c>
       <c r="B79" t="n">
-        <v>13.46309947967529</v>
+        <v>13.46309661865234</v>
       </c>
       <c r="C79" t="n">
         <v>24.72999954223633</v>
@@ -2144,7 +2144,7 @@
         <v>41121</v>
       </c>
       <c r="B80" t="n">
-        <v>16.34298706054688</v>
+        <v>16.34299278259277</v>
       </c>
       <c r="C80" t="n">
         <v>30.02000045776367</v>
@@ -2202,7 +2202,7 @@
         <v>41182</v>
       </c>
       <c r="B82" t="n">
-        <v>17.01931190490723</v>
+        <v>17.01931953430176</v>
       </c>
       <c r="C82" t="n">
         <v>30.95999908447266</v>
@@ -2231,7 +2231,7 @@
         <v>41213</v>
       </c>
       <c r="B83" t="n">
-        <v>15.02383995056152</v>
+        <v>15.02383708953857</v>
       </c>
       <c r="C83" t="n">
         <v>27.32999992370605</v>
@@ -2289,7 +2289,7 @@
         <v>41274</v>
       </c>
       <c r="B85" t="n">
-        <v>17.12938499450684</v>
+        <v>17.1293888092041</v>
       </c>
       <c r="C85" t="n">
         <v>30.42000007629395</v>
@@ -2318,7 +2318,7 @@
         <v>41305</v>
       </c>
       <c r="B86" t="n">
-        <v>19.13400459289551</v>
+        <v>19.13401222229004</v>
       </c>
       <c r="C86" t="n">
         <v>33.97999954223633</v>
@@ -2347,7 +2347,7 @@
         <v>41333</v>
       </c>
       <c r="B87" t="n">
-        <v>18.10917091369629</v>
+        <v>18.10917282104492</v>
       </c>
       <c r="C87" t="n">
         <v>32.15999984741211</v>
@@ -2376,7 +2376,7 @@
         <v>41364</v>
       </c>
       <c r="B88" t="n">
-        <v>20.58679962158203</v>
+        <v>20.58679389953613</v>
       </c>
       <c r="C88" t="n">
         <v>36.56000137329102</v>
@@ -2405,7 +2405,7 @@
         <v>41394</v>
       </c>
       <c r="B89" t="n">
-        <v>20.66562843322754</v>
+        <v>20.6656322479248</v>
       </c>
       <c r="C89" t="n">
         <v>36.70000076293945</v>
@@ -2434,7 +2434,7 @@
         <v>41425</v>
       </c>
       <c r="B90" t="n">
-        <v>24.48794364929199</v>
+        <v>24.48794555664062</v>
       </c>
       <c r="C90" t="n">
         <v>43.08000183105469</v>
@@ -2463,7 +2463,7 @@
         <v>41455</v>
       </c>
       <c r="B91" t="n">
-        <v>25.48269844055176</v>
+        <v>25.48270797729492</v>
       </c>
       <c r="C91" t="n">
         <v>44.83000183105469</v>
@@ -2521,7 +2521,7 @@
         <v>41517</v>
       </c>
       <c r="B93" t="n">
-        <v>21.98549270629883</v>
+        <v>21.98549461364746</v>
       </c>
       <c r="C93" t="n">
         <v>38.31999969482422</v>
@@ -2579,7 +2579,7 @@
         <v>41578</v>
       </c>
       <c r="B95" t="n">
-        <v>27.93511581420898</v>
+        <v>27.93511962890625</v>
       </c>
       <c r="C95" t="n">
         <v>48.68999862670898</v>
@@ -2608,7 +2608,7 @@
         <v>41608</v>
       </c>
       <c r="B96" t="n">
-        <v>28.38776969909668</v>
+        <v>28.38775444030762</v>
       </c>
       <c r="C96" t="n">
         <v>49.04000091552734</v>
@@ -2637,7 +2637,7 @@
         <v>41639</v>
       </c>
       <c r="B97" t="n">
-        <v>32.50933074951172</v>
+        <v>32.50931167602539</v>
       </c>
       <c r="C97" t="n">
         <v>56.15999984741211</v>
@@ -2695,7 +2695,7 @@
         <v>41698</v>
       </c>
       <c r="B99" t="n">
-        <v>30.47806930541992</v>
+        <v>30.47806358337402</v>
       </c>
       <c r="C99" t="n">
         <v>52.18999862670898</v>
@@ -2724,7 +2724,7 @@
         <v>41729</v>
       </c>
       <c r="B100" t="n">
-        <v>32.79647445678711</v>
+        <v>32.79650115966797</v>
       </c>
       <c r="C100" t="n">
         <v>56.15999984741211</v>
@@ -2753,7 +2753,7 @@
         <v>41759</v>
       </c>
       <c r="B101" t="n">
-        <v>30.70582580566406</v>
+        <v>30.7058162689209</v>
       </c>
       <c r="C101" t="n">
         <v>52.58000183105469</v>
@@ -2782,7 +2782,7 @@
         <v>41790</v>
       </c>
       <c r="B102" t="n">
-        <v>31.65206527709961</v>
+        <v>31.65208435058594</v>
       </c>
       <c r="C102" t="n">
         <v>53.72999954223633</v>
@@ -2811,7 +2811,7 @@
         <v>41820</v>
       </c>
       <c r="B103" t="n">
-        <v>33.47238540649414</v>
+        <v>33.47238922119141</v>
       </c>
       <c r="C103" t="n">
         <v>56.81999969482422</v>
@@ -2898,7 +2898,7 @@
         <v>41912</v>
       </c>
       <c r="B106" t="n">
-        <v>33.99220657348633</v>
+        <v>33.99221801757812</v>
       </c>
       <c r="C106" t="n">
         <v>57.27000045776367</v>
@@ -2927,7 +2927,7 @@
         <v>41943</v>
       </c>
       <c r="B107" t="n">
-        <v>37.29232025146484</v>
+        <v>37.29231643676758</v>
       </c>
       <c r="C107" t="n">
         <v>62.83000183105469</v>
@@ -2956,7 +2956,7 @@
         <v>41973</v>
       </c>
       <c r="B108" t="n">
-        <v>39.5743522644043</v>
+        <v>39.57435989379883</v>
       </c>
       <c r="C108" t="n">
         <v>66.11000061035156</v>
@@ -2985,7 +2985,7 @@
         <v>42004</v>
       </c>
       <c r="B109" t="n">
-        <v>39.80781555175781</v>
+        <v>39.80780792236328</v>
       </c>
       <c r="C109" t="n">
         <v>66.5</v>
@@ -3014,7 +3014,7 @@
         <v>42035</v>
       </c>
       <c r="B110" t="n">
-        <v>33.78574371337891</v>
+        <v>33.7857551574707</v>
       </c>
       <c r="C110" t="n">
         <v>56.43999862670898</v>
@@ -3072,7 +3072,7 @@
         <v>42094</v>
       </c>
       <c r="B112" t="n">
-        <v>31.42679214477539</v>
+        <v>31.42679023742676</v>
       </c>
       <c r="C112" t="n">
         <v>52.02999877929688</v>
@@ -3101,7 +3101,7 @@
         <v>42124</v>
       </c>
       <c r="B113" t="n">
-        <v>35.79525375366211</v>
+        <v>35.79526138305664</v>
       </c>
       <c r="C113" t="n">
         <v>58.72000122070312</v>
@@ -3130,7 +3130,7 @@
         <v>42155</v>
       </c>
       <c r="B114" t="n">
-        <v>33.917724609375</v>
+        <v>33.91771697998047</v>
       </c>
       <c r="C114" t="n">
         <v>55.63999938964844</v>
@@ -3159,7 +3159,7 @@
         <v>42185</v>
       </c>
       <c r="B115" t="n">
-        <v>28.95562744140625</v>
+        <v>28.95564079284668</v>
       </c>
       <c r="C115" t="n">
         <v>47.5</v>
@@ -3188,7 +3188,7 @@
         <v>42216</v>
       </c>
       <c r="B116" t="n">
-        <v>30.84537696838379</v>
+        <v>30.84536743164062</v>
       </c>
       <c r="C116" t="n">
         <v>50.59999847412109</v>
@@ -3217,7 +3217,7 @@
         <v>42247</v>
       </c>
       <c r="B117" t="n">
-        <v>31.66623497009277</v>
+        <v>31.66624069213867</v>
       </c>
       <c r="C117" t="n">
         <v>51.40000152587891</v>
@@ -3246,7 +3246,7 @@
         <v>42277</v>
       </c>
       <c r="B118" t="n">
-        <v>27.60013961791992</v>
+        <v>27.60014915466309</v>
       </c>
       <c r="C118" t="n">
         <v>44.79999923706055</v>
@@ -3275,7 +3275,7 @@
         <v>42308</v>
       </c>
       <c r="B119" t="n">
-        <v>23.44780731201172</v>
+        <v>23.44780158996582</v>
       </c>
       <c r="C119" t="n">
         <v>38.06000137329102</v>
@@ -3304,7 +3304,7 @@
         <v>42338</v>
       </c>
       <c r="B120" t="n">
-        <v>22.49273300170898</v>
+        <v>22.49273490905762</v>
       </c>
       <c r="C120" t="n">
         <v>35.93999862670898</v>
@@ -3333,7 +3333,7 @@
         <v>42369</v>
       </c>
       <c r="B121" t="n">
-        <v>22.94334983825684</v>
+        <v>22.9433422088623</v>
       </c>
       <c r="C121" t="n">
         <v>36.65999984741211</v>
@@ -3362,7 +3362,7 @@
         <v>42400</v>
       </c>
       <c r="B122" t="n">
-        <v>18.18069267272949</v>
+        <v>18.18068885803223</v>
       </c>
       <c r="C122" t="n">
         <v>29.04999923706055</v>
@@ -3391,7 +3391,7 @@
         <v>42429</v>
       </c>
       <c r="B123" t="n">
-        <v>20.01816749572754</v>
+        <v>20.01816368103027</v>
       </c>
       <c r="C123" t="n">
         <v>31.36000061035156</v>
@@ -3420,7 +3420,7 @@
         <v>42460</v>
       </c>
       <c r="B124" t="n">
-        <v>21.99062156677246</v>
+        <v>21.99061965942383</v>
       </c>
       <c r="C124" t="n">
         <v>34.45000076293945</v>
@@ -3449,7 +3449,7 @@
         <v>42490</v>
       </c>
       <c r="B125" t="n">
-        <v>13.89653873443604</v>
+        <v>13.89653778076172</v>
       </c>
       <c r="C125" t="n">
         <v>21.77000045776367</v>
@@ -3478,7 +3478,7 @@
         <v>42521</v>
       </c>
       <c r="B126" t="n">
-        <v>14.86896419525146</v>
+        <v>14.86895561218262</v>
       </c>
       <c r="C126" t="n">
         <v>22.55999946594238</v>
@@ -3507,7 +3507,7 @@
         <v>42551</v>
       </c>
       <c r="B127" t="n">
-        <v>16.05531883239746</v>
+        <v>16.05531692504883</v>
       </c>
       <c r="C127" t="n">
         <v>24.36000061035156</v>
@@ -3536,7 +3536,7 @@
         <v>42582</v>
       </c>
       <c r="B128" t="n">
-        <v>21.11049461364746</v>
+        <v>21.11049652099609</v>
       </c>
       <c r="C128" t="n">
         <v>32.02999877929688</v>
@@ -3565,7 +3565,7 @@
         <v>42613</v>
       </c>
       <c r="B129" t="n">
-        <v>22.2375373840332</v>
+        <v>22.23753929138184</v>
       </c>
       <c r="C129" t="n">
         <v>33.7400016784668</v>
@@ -3594,7 +3594,7 @@
         <v>42643</v>
       </c>
       <c r="B130" t="n">
-        <v>25.85522651672363</v>
+        <v>25.85522270202637</v>
       </c>
       <c r="C130" t="n">
         <v>38.54999923706055</v>
@@ -3623,7 +3623,7 @@
         <v>42674</v>
       </c>
       <c r="B131" t="n">
-        <v>23.01148796081543</v>
+        <v>23.0114860534668</v>
       </c>
       <c r="C131" t="n">
         <v>34.31000137329102</v>
@@ -3652,7 +3652,7 @@
         <v>42704</v>
       </c>
       <c r="B132" t="n">
-        <v>26.89480972290039</v>
+        <v>26.89479827880859</v>
       </c>
       <c r="C132" t="n">
         <v>40.09999847412109</v>
@@ -3681,7 +3681,7 @@
         <v>42735</v>
       </c>
       <c r="B133" t="n">
-        <v>26.01960182189941</v>
+        <v>26.01960945129395</v>
       </c>
       <c r="C133" t="n">
         <v>38.16999816894531</v>
@@ -3710,7 +3710,7 @@
         <v>42766</v>
       </c>
       <c r="B134" t="n">
-        <v>30.7777156829834</v>
+        <v>30.77771377563477</v>
       </c>
       <c r="C134" t="n">
         <v>45.15000152587891</v>
@@ -3768,7 +3768,7 @@
         <v>42825</v>
       </c>
       <c r="B136" t="n">
-        <v>31.73599433898926</v>
+        <v>31.73599243164062</v>
       </c>
       <c r="C136" t="n">
         <v>45.93000030517578</v>
@@ -3797,7 +3797,7 @@
         <v>42855</v>
       </c>
       <c r="B137" t="n">
-        <v>29.11033058166504</v>
+        <v>29.11033630371094</v>
       </c>
       <c r="C137" t="n">
         <v>42.13000106811523</v>
@@ -3826,7 +3826,7 @@
         <v>42886</v>
       </c>
       <c r="B138" t="n">
-        <v>30.10531234741211</v>
+        <v>30.10531997680664</v>
       </c>
       <c r="C138" t="n">
         <v>43.56999969482422</v>
@@ -3855,7 +3855,7 @@
         <v>42916</v>
       </c>
       <c r="B139" t="n">
-        <v>27.18231391906738</v>
+        <v>27.18230628967285</v>
       </c>
       <c r="C139" t="n">
         <v>38.75</v>
@@ -3884,7 +3884,7 @@
         <v>42947</v>
       </c>
       <c r="B140" t="n">
-        <v>23.12075424194336</v>
+        <v>23.12075042724609</v>
       </c>
       <c r="C140" t="n">
         <v>32.95999908447266</v>
@@ -3942,7 +3942,7 @@
         <v>43008</v>
       </c>
       <c r="B142" t="n">
-        <v>23.71375274658203</v>
+        <v>23.71375465393066</v>
       </c>
       <c r="C142" t="n">
         <v>33.16999816894531</v>
@@ -3971,7 +3971,7 @@
         <v>43039</v>
       </c>
       <c r="B143" t="n">
-        <v>26.43043899536133</v>
+        <v>26.43044281005859</v>
       </c>
       <c r="C143" t="n">
         <v>36.97000122070312</v>
@@ -4000,7 +4000,7 @@
         <v>43069</v>
       </c>
       <c r="B144" t="n">
-        <v>27.56715393066406</v>
+        <v>27.56715202331543</v>
       </c>
       <c r="C144" t="n">
         <v>38.56000137329102</v>
@@ -4029,7 +4029,7 @@
         <v>43100</v>
       </c>
       <c r="B145" t="n">
-        <v>30.35694694519043</v>
+        <v>30.35694122314453</v>
       </c>
       <c r="C145" t="n">
         <v>41.84000015258789</v>
@@ -4087,7 +4087,7 @@
         <v>43159</v>
       </c>
       <c r="B147" t="n">
-        <v>38.74428558349609</v>
+        <v>38.74428176879883</v>
       </c>
       <c r="C147" t="n">
         <v>53.40000152587891</v>
@@ -4145,7 +4145,7 @@
         <v>43220</v>
       </c>
       <c r="B149" t="n">
-        <v>42.44471740722656</v>
+        <v>42.44472503662109</v>
       </c>
       <c r="C149" t="n">
         <v>57.88999938964844</v>
@@ -4174,7 +4174,7 @@
         <v>43251</v>
       </c>
       <c r="B150" t="n">
-        <v>41.31558609008789</v>
+        <v>41.31559371948242</v>
       </c>
       <c r="C150" t="n">
         <v>56.34999847412109</v>
@@ -4203,7 +4203,7 @@
         <v>43281</v>
       </c>
       <c r="B151" t="n">
-        <v>41.85061264038086</v>
+        <v>41.85060882568359</v>
       </c>
       <c r="C151" t="n">
         <v>56.47000122070312</v>
@@ -4261,7 +4261,7 @@
         <v>43343</v>
       </c>
       <c r="B153" t="n">
-        <v>39.67914581298828</v>
+        <v>39.67915344238281</v>
       </c>
       <c r="C153" t="n">
         <v>53.54000091552734</v>
@@ -4290,7 +4290,7 @@
         <v>43373</v>
       </c>
       <c r="B154" t="n">
-        <v>35.5589599609375</v>
+        <v>35.55896377563477</v>
       </c>
       <c r="C154" t="n">
         <v>47.34999847412109</v>
@@ -4319,7 +4319,7 @@
         <v>43404</v>
       </c>
       <c r="B155" t="n">
-        <v>30.21197509765625</v>
+        <v>30.21196937561035</v>
       </c>
       <c r="C155" t="n">
         <v>40.22999954223633</v>
@@ -4377,7 +4377,7 @@
         <v>43465</v>
       </c>
       <c r="B157" t="n">
-        <v>29.47649192810059</v>
+        <v>29.47649765014648</v>
       </c>
       <c r="C157" t="n">
         <v>38.59000015258789</v>
@@ -4406,7 +4406,7 @@
         <v>43496</v>
       </c>
       <c r="B158" t="n">
-        <v>33.82271957397461</v>
+        <v>33.82272338867188</v>
       </c>
       <c r="C158" t="n">
         <v>44.27999877929688</v>
@@ -4435,7 +4435,7 @@
         <v>43524</v>
       </c>
       <c r="B159" t="n">
-        <v>35.56428146362305</v>
+        <v>35.56428527832031</v>
       </c>
       <c r="C159" t="n">
         <v>46.56000137329102</v>
@@ -4464,7 +4464,7 @@
         <v>43555</v>
       </c>
       <c r="B160" t="n">
-        <v>37.06504821777344</v>
+        <v>37.06504058837891</v>
       </c>
       <c r="C160" t="n">
         <v>47.88999938964844</v>
@@ -4493,7 +4493,7 @@
         <v>43585</v>
       </c>
       <c r="B161" t="n">
-        <v>37.39786148071289</v>
+        <v>37.39785385131836</v>
       </c>
       <c r="C161" t="n">
         <v>48.31999969482422</v>
@@ -4551,7 +4551,7 @@
         <v>43646</v>
       </c>
       <c r="B163" t="n">
-        <v>36.99448776245117</v>
+        <v>36.9944953918457</v>
       </c>
       <c r="C163" t="n">
         <v>47.11999893188477</v>
@@ -4580,7 +4580,7 @@
         <v>43677</v>
       </c>
       <c r="B164" t="n">
-        <v>36.35855102539062</v>
+        <v>36.35854721069336</v>
       </c>
       <c r="C164" t="n">
         <v>46.31000137329102</v>
@@ -4609,7 +4609,7 @@
         <v>43708</v>
       </c>
       <c r="B165" t="n">
-        <v>39.42049026489258</v>
+        <v>39.42048263549805</v>
       </c>
       <c r="C165" t="n">
         <v>50.20999908447266</v>
@@ -4638,7 +4638,7 @@
         <v>43738</v>
       </c>
       <c r="B166" t="n">
-        <v>42.74166488647461</v>
+        <v>42.74165725708008</v>
       </c>
       <c r="C166" t="n">
         <v>53.79000091552734</v>
@@ -4696,7 +4696,7 @@
         <v>43799</v>
       </c>
       <c r="B168" t="n">
-        <v>47.42187881469727</v>
+        <v>47.42185974121094</v>
       </c>
       <c r="C168" t="n">
         <v>59.68000030517578</v>
@@ -4725,7 +4725,7 @@
         <v>43830</v>
       </c>
       <c r="B169" t="n">
-        <v>47.79343032836914</v>
+        <v>47.79343795776367</v>
       </c>
       <c r="C169" t="n">
         <v>59.5</v>
@@ -4754,7 +4754,7 @@
         <v>43861</v>
       </c>
       <c r="B170" t="n">
-        <v>45.77727127075195</v>
+        <v>45.77726364135742</v>
       </c>
       <c r="C170" t="n">
         <v>56.9900016784668</v>
@@ -4783,7 +4783,7 @@
         <v>43890</v>
       </c>
       <c r="B171" t="n">
-        <v>38.51589202880859</v>
+        <v>38.5158805847168</v>
       </c>
       <c r="C171" t="n">
         <v>47.95000076293945</v>
@@ -4870,7 +4870,7 @@
         <v>43982</v>
       </c>
       <c r="B174" t="n">
-        <v>43.29450225830078</v>
+        <v>43.29450607299805</v>
       </c>
       <c r="C174" t="n">
         <v>53.04000091552734</v>
@@ -4899,7 +4899,7 @@
         <v>44012</v>
       </c>
       <c r="B175" t="n">
-        <v>40.0262451171875</v>
+        <v>40.02625274658203</v>
       </c>
       <c r="C175" t="n">
         <v>48.40999984741211</v>
@@ -4928,7 +4928,7 @@
         <v>44043</v>
       </c>
       <c r="B176" t="n">
-        <v>37.38870620727539</v>
+        <v>37.38871002197266</v>
       </c>
       <c r="C176" t="n">
         <v>45.22000122070312</v>
@@ -5015,7 +5015,7 @@
         <v>44135</v>
       </c>
       <c r="B179" t="n">
-        <v>40.07857131958008</v>
+        <v>40.07857894897461</v>
       </c>
       <c r="C179" t="n">
         <v>47.81999969482422</v>
@@ -5044,7 +5044,7 @@
         <v>44165</v>
       </c>
       <c r="B180" t="n">
-        <v>49.2894401550293</v>
+        <v>49.28943634033203</v>
       </c>
       <c r="C180" t="n">
         <v>58.81000137329102</v>
@@ -5102,7 +5102,7 @@
         <v>44227</v>
       </c>
       <c r="B182" t="n">
-        <v>55.99276351928711</v>
+        <v>55.99275588989258</v>
       </c>
       <c r="C182" t="n">
         <v>66.12000274658203</v>
@@ -5131,7 +5131,7 @@
         <v>44255</v>
       </c>
       <c r="B183" t="n">
-        <v>62.01375579833984</v>
+        <v>62.01375961303711</v>
       </c>
       <c r="C183" t="n">
         <v>73.23000335693359</v>
@@ -5160,7 +5160,7 @@
         <v>44286</v>
       </c>
       <c r="B184" t="n">
-        <v>65.57312774658203</v>
+        <v>65.57315063476562</v>
       </c>
       <c r="C184" t="n">
         <v>76.75</v>
@@ -5189,7 +5189,7 @@
         <v>44316</v>
       </c>
       <c r="B185" t="n">
-        <v>79.32000732421875</v>
+        <v>79.32002258300781</v>
       </c>
       <c r="C185" t="n">
         <v>92.83999633789062</v>
@@ -5218,7 +5218,7 @@
         <v>44347</v>
       </c>
       <c r="B186" t="n">
-        <v>82.41987609863281</v>
+        <v>82.41989135742188</v>
       </c>
       <c r="C186" t="n">
         <v>95.75</v>
@@ -5276,7 +5276,7 @@
         <v>44408</v>
       </c>
       <c r="B188" t="n">
-        <v>75.66273498535156</v>
+        <v>75.66274261474609</v>
       </c>
       <c r="C188" t="n">
         <v>87.90000152587891</v>
@@ -5305,7 +5305,7 @@
         <v>44439</v>
       </c>
       <c r="B189" t="n">
-        <v>75.39590454101562</v>
+        <v>75.39588928222656</v>
       </c>
       <c r="C189" t="n">
         <v>87.58999633789062</v>
@@ -5334,7 +5334,7 @@
         <v>44469</v>
       </c>
       <c r="B190" t="n">
-        <v>71.61013793945312</v>
+        <v>71.61013031005859</v>
       </c>
       <c r="C190" t="n">
         <v>82.51999664306641</v>
@@ -5363,7 +5363,7 @@
         <v>44500</v>
       </c>
       <c r="B191" t="n">
-        <v>77.29417419433594</v>
+        <v>77.29415893554688</v>
       </c>
       <c r="C191" t="n">
         <v>89.06999969482422</v>
@@ -5392,7 +5392,7 @@
         <v>44530</v>
       </c>
       <c r="B192" t="n">
-        <v>89.09613037109375</v>
+        <v>89.09613800048828</v>
       </c>
       <c r="C192" t="n">
         <v>102.6699981689453</v>
@@ -5421,7 +5421,7 @@
         <v>44561</v>
       </c>
       <c r="B193" t="n">
-        <v>98.70025634765625</v>
+        <v>98.70024871826172</v>
       </c>
       <c r="C193" t="n">
         <v>112.9800033569336</v>
@@ -5450,7 +5450,7 @@
         <v>44592</v>
       </c>
       <c r="B194" t="n">
-        <v>93.60710906982422</v>
+        <v>93.60711669921875</v>
       </c>
       <c r="C194" t="n">
         <v>107.1500015258789</v>
@@ -5479,7 +5479,7 @@
         <v>44620</v>
       </c>
       <c r="B195" t="n">
-        <v>90.12142181396484</v>
+        <v>90.12143707275391</v>
       </c>
       <c r="C195" t="n">
         <v>103.1600036621094</v>
@@ -5537,7 +5537,7 @@
         <v>44681</v>
       </c>
       <c r="B197" t="n">
-        <v>72.20670318603516</v>
+        <v>72.20669555664062</v>
       </c>
       <c r="C197" t="n">
         <v>82.04000091552734</v>
@@ -5566,7 +5566,7 @@
         <v>44712</v>
       </c>
       <c r="B198" t="n">
-        <v>74.52145385742188</v>
+        <v>74.52147674560547</v>
       </c>
       <c r="C198" t="n">
         <v>84.66999816894531</v>
@@ -5595,7 +5595,7 @@
         <v>44742</v>
       </c>
       <c r="B199" t="n">
-        <v>63.49800491333008</v>
+        <v>63.49800872802734</v>
       </c>
       <c r="C199" t="n">
         <v>71.44000244140625</v>
@@ -5653,7 +5653,7 @@
         <v>44804</v>
       </c>
       <c r="B201" t="n">
-        <v>59.51604461669922</v>
+        <v>59.51605224609375</v>
       </c>
       <c r="C201" t="n">
         <v>66.95999908447266</v>
@@ -5682,7 +5682,7 @@
         <v>44834</v>
       </c>
       <c r="B202" t="n">
-        <v>47.85250854492188</v>
+        <v>47.85251235961914</v>
       </c>
       <c r="C202" t="n">
         <v>53.22999954223633</v>
@@ -5711,7 +5711,7 @@
         <v>44865</v>
       </c>
       <c r="B203" t="n">
-        <v>44.64316940307617</v>
+        <v>44.64316558837891</v>
       </c>
       <c r="C203" t="n">
         <v>49.65999984741211</v>
@@ -5740,7 +5740,7 @@
         <v>44895</v>
       </c>
       <c r="B204" t="n">
-        <v>47.61877059936523</v>
+        <v>47.61877822875977</v>
       </c>
       <c r="C204" t="n">
         <v>52.97000122070312</v>
@@ -5769,7 +5769,7 @@
         <v>44926</v>
       </c>
       <c r="B205" t="n">
-        <v>47.95346832275391</v>
+        <v>47.95346450805664</v>
       </c>
       <c r="C205" t="n">
         <v>52.61000061035156</v>
@@ -5798,7 +5798,7 @@
         <v>44957</v>
       </c>
       <c r="B206" t="n">
-        <v>61.78076553344727</v>
+        <v>61.78073883056641</v>
       </c>
       <c r="C206" t="n">
         <v>67.77999877929688</v>
@@ -5856,7 +5856,7 @@
         <v>45016</v>
       </c>
       <c r="B208" t="n">
-        <v>60.95523071289062</v>
+        <v>60.95522689819336</v>
       </c>
       <c r="C208" t="n">
         <v>66.12000274658203</v>
@@ -5885,7 +5885,7 @@
         <v>45046</v>
       </c>
       <c r="B209" t="n">
-        <v>54.17934417724609</v>
+        <v>54.17934036254883</v>
       </c>
       <c r="C209" t="n">
         <v>58.77000045776367</v>
@@ -5912,7 +5912,7 @@
         <v>45077</v>
       </c>
       <c r="B210" t="n">
-        <v>55.40545654296875</v>
+        <v>55.40544891357422</v>
       </c>
       <c r="C210" t="n">
         <v>60.09999847412109</v>
@@ -5939,7 +5939,7 @@
         <v>45107</v>
       </c>
       <c r="B211" t="n">
-        <v>57.66496658325195</v>
+        <v>57.66496276855469</v>
       </c>
       <c r="C211" t="n">
         <v>61.86999893188477</v>
@@ -5966,7 +5966,7 @@
         <v>45138</v>
       </c>
       <c r="B212" t="n">
-        <v>59.18418502807617</v>
+        <v>59.18418884277344</v>
       </c>
       <c r="C212" t="n">
         <v>63.5</v>
@@ -5993,7 +5993,7 @@
         <v>45169</v>
       </c>
       <c r="B213" t="n">
-        <v>65.97870635986328</v>
+        <v>65.97871398925781</v>
       </c>
       <c r="C213" t="n">
         <v>70.79000091552734</v>
@@ -6020,7 +6020,7 @@
         <v>45199</v>
       </c>
       <c r="B214" t="n">
-        <v>62.12759399414062</v>
+        <v>62.12760543823242</v>
       </c>
       <c r="C214" t="n">
         <v>65.94999694824219</v>
@@ -6047,7 +6047,7 @@
         <v>45230</v>
       </c>
       <c r="B215" t="n">
-        <v>64.29428100585938</v>
+        <v>64.29428863525391</v>
       </c>
       <c r="C215" t="n">
         <v>68.25</v>
@@ -6074,7 +6074,7 @@
         <v>45260</v>
       </c>
       <c r="B216" t="n">
-        <v>74.51542663574219</v>
+        <v>74.51543426513672</v>
       </c>
       <c r="C216" t="n">
         <v>79.09999847412109</v>
@@ -6101,7 +6101,7 @@
         <v>45291</v>
       </c>
       <c r="B217" t="n">
-        <v>81.09866333007812</v>
+        <v>81.09864807128906</v>
       </c>
       <c r="C217" t="n">
         <v>85.37000274658203</v>
@@ -6128,7 +6128,7 @@
         <v>45322</v>
       </c>
       <c r="B218" t="n">
-        <v>81.39314270019531</v>
+        <v>81.39315032958984</v>
       </c>
       <c r="C218" t="n">
         <v>85.68000030517578</v>
@@ -6182,7 +6182,7 @@
         <v>45382</v>
       </c>
       <c r="B220" t="n">
-        <v>89.11498260498047</v>
+        <v>89.114990234375</v>
       </c>
       <c r="C220" t="n">
         <v>93.05000305175781</v>
@@ -6236,7 +6236,7 @@
         <v>45443</v>
       </c>
       <c r="B222" t="n">
-        <v>89.29694366455078</v>
+        <v>89.29693603515625</v>
       </c>
       <c r="C222" t="n">
         <v>93.23999786376953</v>
@@ -6263,7 +6263,7 @@
         <v>45473</v>
       </c>
       <c r="B223" t="n">
-        <v>99.56031799316406</v>
+        <v>99.56032562255859</v>
       </c>
       <c r="C223" t="n">
         <v>103.2699966430664</v>
@@ -6317,7 +6317,7 @@
         <v>45535</v>
       </c>
       <c r="B225" t="n">
-        <v>95.97395324707031</v>
+        <v>95.97394561767578</v>
       </c>
       <c r="C225" t="n">
         <v>99.55000305175781</v>
@@ -6375,7 +6375,7 @@
         <v>45596</v>
       </c>
       <c r="B227" t="n">
-        <v>97.41554260253906</v>
+        <v>97.41555023193359</v>
       </c>
       <c r="C227" t="n">
         <v>100.370002746582</v>
@@ -6404,7 +6404,7 @@
         <v>45626</v>
       </c>
       <c r="B228" t="n">
-        <v>98.3472900390625</v>
+        <v>98.34729766845703</v>
       </c>
       <c r="C228" t="n">
         <v>101.3300018310547</v>
@@ -6462,7 +6462,7 @@
         <v>45688</v>
       </c>
       <c r="B230" t="n">
-        <v>94.21836090087891</v>
+        <v>94.21835327148438</v>
       </c>
       <c r="C230" t="n">
         <v>96.36000061035156</v>
@@ -6520,7 +6520,7 @@
         <v>45747</v>
       </c>
       <c r="B232" t="n">
-        <v>83.74215698242188</v>
+        <v>83.74214935302734</v>
       </c>
       <c r="C232" t="n">
         <v>84.94999694824219</v>
@@ -6549,7 +6549,7 @@
         <v>45777</v>
       </c>
       <c r="B233" t="n">
-        <v>89.73571014404297</v>
+        <v>89.7357177734375</v>
       </c>
       <c r="C233" t="n">
         <v>91.02999877929688</v>
@@ -6607,7 +6607,7 @@
         <v>45838</v>
       </c>
       <c r="B235" t="n">
-        <v>143.0334014892578</v>
+        <v>143.0333862304688</v>
       </c>
       <c r="C235" t="n">
         <v>144.3300018310547</v>
@@ -6810,7 +6810,7 @@
         <v>46053</v>
       </c>
       <c r="B242" t="n">
-        <v>406.3643493652344</v>
+        <v>406.3643188476562</v>
       </c>
       <c r="C242" t="n">
         <v>407.6900024414062</v>
@@ -6839,7 +6839,7 @@
         <v>46081</v>
       </c>
       <c r="B243" t="n">
-        <v>406.5138244628906</v>
+        <v>406.5138549804688</v>
       </c>
       <c r="C243" t="n">
         <v>407.8399963378906</v>
